--- a/AUTOMOTIVO.xlsx
+++ b/AUTOMOTIVO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUDESCHA\Downloads\Dashaboard em HTML\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemininar-my.sharepoint.com/personal/guilherme_deschamps_capgemini_com/Documents/Documents/INVOICE/DASHBOARD/AUTOMOTIVO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E24B7CA-03EC-439C-BC6E-D2D9F79CC7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{519F2E90-BF14-445A-9765-AB404186F25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0846D51-A337-4AF3-9397-D975265F6CDD}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39811114-C66D-43D9-8E26-15996D34E7BD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="371">
   <si>
     <t>ASV Ref Id</t>
   </si>
@@ -122,16 +122,19 @@
     <t>B71378</t>
   </si>
   <si>
-    <t>B72607</t>
-  </si>
-  <si>
-    <t>EP1725073</t>
-  </si>
-  <si>
-    <t>Israel Correa</t>
-  </si>
-  <si>
-    <t>15233.36</t>
+    <t>13243.82</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202604281912570977</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85504514PO</t>
+  </si>
+  <si>
+    <t>2026-04-28 19:12:57.203</t>
+  </si>
+  <si>
+    <t>22688889000384&amp;25/11/2025&amp;</t>
   </si>
   <si>
     <t>SKFAUTOAPE202607011622160651</t>
@@ -173,7 +176,7 @@
     <t>Query Raised</t>
   </si>
   <si>
-    <t>22688889000346&amp;31/07/2026</t>
+    <t>Pedido não informado</t>
   </si>
   <si>
     <t>SKFAUTOAPE202607071916200103</t>
@@ -200,6 +203,9 @@
     <t>Status NF</t>
   </si>
   <si>
+    <t>17.09</t>
+  </si>
+  <si>
     <t>14.01</t>
   </si>
   <si>
@@ -212,30 +218,6 @@
     <t>01.07</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202606301455080352</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85520691PO</t>
-  </si>
-  <si>
-    <t>2026-06-30 14:55:08.813</t>
-  </si>
-  <si>
-    <t>660.00</t>
-  </si>
-  <si>
-    <t>45662885000122&amp;NA</t>
-  </si>
-  <si>
-    <t>14.02</t>
-  </si>
-  <si>
-    <t>B72620</t>
-  </si>
-  <si>
-    <t>EP1635130</t>
-  </si>
-  <si>
     <t>Caroline Diniz Silva</t>
   </si>
   <si>
@@ -245,31 +227,13 @@
     <t>B71364</t>
   </si>
   <si>
-    <t>17.05</t>
+    <t>Mary Ellen Silva</t>
   </si>
   <si>
     <t>Pedido sem saldo</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608031947410234</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85530903PO</t>
-  </si>
-  <si>
-    <t>2026-08-03 19:47:42.053</t>
-  </si>
-  <si>
-    <t>22688889000346&amp;01/09/2026</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608031948010235</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85530904PO</t>
-  </si>
-  <si>
-    <t>2026-08-03 19:48:01.507</t>
+    <t>Arthur Castilho</t>
   </si>
   <si>
     <t>Andre Bisetto</t>
@@ -278,6 +242,72 @@
     <t>Thalles Miranda</t>
   </si>
   <si>
+    <t>SKFAUTOAPE202604281910290968</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85504505PO</t>
+  </si>
+  <si>
+    <t>2026-04-28 19:10:30.113</t>
+  </si>
+  <si>
+    <t>138055.00</t>
+  </si>
+  <si>
+    <t>28314811000186&amp;07/01/2026&amp;</t>
+  </si>
+  <si>
+    <t>B71419</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202607301850030538</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85529990PO</t>
+  </si>
+  <si>
+    <t>2026-07-30 18:50:03.247</t>
+  </si>
+  <si>
+    <t>31736.08</t>
+  </si>
+  <si>
+    <t>00603542000230&amp;NA&amp;</t>
+  </si>
+  <si>
+    <t>08.02</t>
+  </si>
+  <si>
+    <t>B68984</t>
+  </si>
+  <si>
+    <t>PR1928606</t>
+  </si>
+  <si>
+    <t>Johnattan Coloro Faria</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608031435170208</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85530787PO</t>
+  </si>
+  <si>
+    <t>2026-08-03 14:35:17.61</t>
+  </si>
+  <si>
+    <t>710.73</t>
+  </si>
+  <si>
+    <t>05018761000194&amp;26/08/2026</t>
+  </si>
+  <si>
+    <t>B72958</t>
+  </si>
+  <si>
+    <t>EP1563083</t>
+  </si>
+  <si>
     <t>SKFAUTOAPE202608042028250327</t>
   </si>
   <si>
@@ -305,15 +335,18 @@
     <t>Daniel H Melo</t>
   </si>
   <si>
+    <t>17.14</t>
+  </si>
+  <si>
+    <t>Emily Viola</t>
+  </si>
+  <si>
     <t>Marinete Pereira</t>
   </si>
   <si>
     <t>HURTH INFER IND. DE MAQ. E FER</t>
   </si>
   <si>
-    <t>LEONARDO TAVARES DA SILVA DE O</t>
-  </si>
-  <si>
     <t>LOGCOMEX S/A</t>
   </si>
   <si>
@@ -323,12 +356,18 @@
     <t>LUCIANA R.C. LEITE MEI</t>
   </si>
   <si>
-    <t>STYLUX BRASIL SIST DE ILU E EN</t>
-  </si>
-  <si>
     <t>EKAIZEN GESTAO EMPRE DIGITAL L</t>
   </si>
   <si>
+    <t>CGM SERVICE NETWORK LTDA - ME</t>
+  </si>
+  <si>
+    <t>DNV BUSI ASSU AVA CERT BRA</t>
+  </si>
+  <si>
+    <t>DI2S-DADOS,INTE INFO SOLU LTDA</t>
+  </si>
+  <si>
     <t>SKFAUTOAPE202602201336050303</t>
   </si>
   <si>
@@ -359,30 +398,6 @@
     <t>Everton Santos</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608101929090258</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85532502PO</t>
-  </si>
-  <si>
-    <t>2026-08-10 19:29:09.837</t>
-  </si>
-  <si>
-    <t>2983.75</t>
-  </si>
-  <si>
-    <t>27770739000210&amp;30/08/2026</t>
-  </si>
-  <si>
-    <t>B72853</t>
-  </si>
-  <si>
-    <t>MUNDIVOX NETWORKS LTDA</t>
-  </si>
-  <si>
-    <t>EP998132</t>
-  </si>
-  <si>
     <t>SKFAUTOAPE202608121250060439</t>
   </si>
   <si>
@@ -431,46 +446,97 @@
     <t>EP358955</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608051958310407</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85531421PO</t>
-  </si>
-  <si>
-    <t>2026-08-05 19:58:31.937</t>
-  </si>
-  <si>
-    <t>1705.88</t>
-  </si>
-  <si>
-    <t>09256824000100&amp;02/12/2026&amp;</t>
-  </si>
-  <si>
-    <t>B69900</t>
-  </si>
-  <si>
-    <t>MW DO BRASIL TERCEIRIZACOES LT</t>
-  </si>
-  <si>
-    <t>EP10719</t>
-  </si>
-  <si>
-    <t>Roberto Ferreira</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608051959090409</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85531423PO</t>
-  </si>
-  <si>
-    <t>2026-08-05 19:59:10.153</t>
-  </si>
-  <si>
-    <t>1978.20</t>
-  </si>
-  <si>
-    <t>Aguardando retorno</t>
+    <t>2318.57</t>
+  </si>
+  <si>
+    <t>B69383</t>
+  </si>
+  <si>
+    <t>SOTREQ S/A</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608121912250447</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85533053PO</t>
+  </si>
+  <si>
+    <t>2026-08-12 19:12:26.09</t>
+  </si>
+  <si>
+    <t>57773.02</t>
+  </si>
+  <si>
+    <t>07768031000136&amp;NA&amp;</t>
+  </si>
+  <si>
+    <t>16.02</t>
+  </si>
+  <si>
+    <t>B72701</t>
+  </si>
+  <si>
+    <t>GERSON &amp; GREY SERVIÇOS LTDA</t>
+  </si>
+  <si>
+    <t>EP7213</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608031225460177</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85530737PO</t>
+  </si>
+  <si>
+    <t>2026-08-03 12:25:46.153</t>
+  </si>
+  <si>
+    <t>14171.56</t>
+  </si>
+  <si>
+    <t>143808&amp;01</t>
+  </si>
+  <si>
+    <t>03774819006054&amp;NA&amp;</t>
+  </si>
+  <si>
+    <t>B72869</t>
+  </si>
+  <si>
+    <t>SERVICO NACIO APRENDI INDUS</t>
+  </si>
+  <si>
+    <t>EP3004</t>
+  </si>
+  <si>
+    <t>Carlos Manoel Da Silva</t>
+  </si>
+  <si>
+    <t>Valor divergente</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608131234430480</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85533195PO</t>
+  </si>
+  <si>
+    <t>2026-08-13 12:34:43.883</t>
+  </si>
+  <si>
+    <t>3284.75</t>
+  </si>
+  <si>
+    <t>04676352000112&amp;15/09/2026</t>
+  </si>
+  <si>
+    <t>B73091</t>
+  </si>
+  <si>
+    <t>ZAKE &amp; RANGEL ADVOGADOS</t>
+  </si>
+  <si>
+    <t>EP12398</t>
   </si>
   <si>
     <t>SKFAUTOAPE202608201946470375</t>
@@ -521,9 +587,6 @@
     <t>Pedido incorreto</t>
   </si>
   <si>
-    <t>Informar pedido novo</t>
-  </si>
-  <si>
     <t>SKFAUTOAPE202608111944250344</t>
   </si>
   <si>
@@ -566,9 +629,6 @@
     <t>Alterar código de mercadoria</t>
   </si>
   <si>
-    <t>Ricardo Alves</t>
-  </si>
-  <si>
     <t>SKFAUTOAPE202608041401390305</t>
   </si>
   <si>
@@ -596,34 +656,502 @@
     <t>EP2067</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202607201751210218</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85526050PO</t>
-  </si>
-  <si>
-    <t>2026-07-20 17:51:21.867</t>
-  </si>
-  <si>
-    <t>37528.42</t>
-  </si>
-  <si>
-    <t>248118&amp;01</t>
-  </si>
-  <si>
-    <t>58069360000120&amp;18/09/2026</t>
-  </si>
-  <si>
-    <t>B73029</t>
-  </si>
-  <si>
-    <t>STEFANINI CONSULTORIA INFO LTD</t>
-  </si>
-  <si>
-    <t>EP1423199</t>
-  </si>
-  <si>
-    <t>Confirmar cancelamento da NF</t>
+    <t>EP13503</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608191509020245</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85534614PO</t>
+  </si>
+  <si>
+    <t>2026-08-19 15:09:02.637</t>
+  </si>
+  <si>
+    <t>429.79</t>
+  </si>
+  <si>
+    <t>07222725000173&amp;28/09/2026&amp;</t>
+  </si>
+  <si>
+    <t>B72029</t>
+  </si>
+  <si>
+    <t>PTA LOCACOES DE EQUIPAMENTOS</t>
+  </si>
+  <si>
+    <t>EP1352515</t>
+  </si>
+  <si>
+    <t>Thiago Fiorini</t>
+  </si>
+  <si>
+    <t>Aprovar serviço</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608202304290392</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535053PO</t>
+  </si>
+  <si>
+    <t>2026-08-20 23:04:29.173</t>
+  </si>
+  <si>
+    <t>34151100002850&amp;NA</t>
+  </si>
+  <si>
+    <t>EP901064</t>
+  </si>
+  <si>
+    <t>Vitor Goncalves</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202607311835050582</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85530424PO</t>
+  </si>
+  <si>
+    <t>2026-07-31 18:35:05.167</t>
+  </si>
+  <si>
+    <t>26293.34</t>
+  </si>
+  <si>
+    <t>00603542000159&amp;23/07/026</t>
+  </si>
+  <si>
+    <t>603542000159</t>
+  </si>
+  <si>
+    <t>EP1584106</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608191506480237</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85534606PO</t>
+  </si>
+  <si>
+    <t>2026-08-19 15:06:49.087</t>
+  </si>
+  <si>
+    <t>50471.40</t>
+  </si>
+  <si>
+    <t>09127054000197&amp;NA&amp;</t>
+  </si>
+  <si>
+    <t>B70897</t>
+  </si>
+  <si>
+    <t>AZ INTELIGEN D NEGOC LTDA ME</t>
+  </si>
+  <si>
+    <t>EP8997</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608191507480241</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85534610PO</t>
+  </si>
+  <si>
+    <t>2026-08-19 15:07:48.263</t>
+  </si>
+  <si>
+    <t>53781.00</t>
+  </si>
+  <si>
+    <t>09127054000197&amp;03/10/2026&amp;</t>
+  </si>
+  <si>
+    <t>17.01</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608201350240360</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85534977PO</t>
+  </si>
+  <si>
+    <t>2026-08-20 13:50:24.77</t>
+  </si>
+  <si>
+    <t>23760.00</t>
+  </si>
+  <si>
+    <t>20918745000141&amp;19/09/2026</t>
+  </si>
+  <si>
+    <t>03.05</t>
+  </si>
+  <si>
+    <t>B73272</t>
+  </si>
+  <si>
+    <t>FELIPE TEIXEIRA PIRES</t>
+  </si>
+  <si>
+    <t>EP13505</t>
+  </si>
+  <si>
+    <t>Confirmar novo pedido</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202607171351260621</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85525659PO</t>
+  </si>
+  <si>
+    <t>2026-07-17 13:51:26.94</t>
+  </si>
+  <si>
+    <t>12424.00</t>
+  </si>
+  <si>
+    <t>14824170000103&amp;31/07/2026</t>
+  </si>
+  <si>
+    <t>EP6563</t>
+  </si>
+  <si>
+    <t>Ajustar pedido para amount</t>
+  </si>
+  <si>
+    <t>DHL EXPRESS</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608181859350157</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85534388PO</t>
+  </si>
+  <si>
+    <t>2026-08-18 18:59:35.983</t>
+  </si>
+  <si>
+    <t>4392.58</t>
+  </si>
+  <si>
+    <t>13182443000273&amp;NA</t>
+  </si>
+  <si>
+    <t>B69099</t>
+  </si>
+  <si>
+    <t>FASTENAL B</t>
+  </si>
+  <si>
+    <t>P120899</t>
+  </si>
+  <si>
+    <t>DNV Business Assurance Avaliações e Certificações Brasil Ltda</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608191343120226</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85534588PO</t>
+  </si>
+  <si>
+    <t>2026-08-19 13:43:13.0</t>
+  </si>
+  <si>
+    <t>4638.72</t>
+  </si>
+  <si>
+    <t>06203366000144&amp;NA&amp;</t>
+  </si>
+  <si>
+    <t>B73218</t>
+  </si>
+  <si>
+    <t>LAVANDERIA ECOLOGY EIRELI</t>
+  </si>
+  <si>
+    <t>EP1696595</t>
+  </si>
+  <si>
+    <t>Luiz dos Santos</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212243310433</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535292PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:43:31.493</t>
+  </si>
+  <si>
+    <t>84466.00</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;05/11/2026</t>
+  </si>
+  <si>
+    <t>11.02</t>
+  </si>
+  <si>
+    <t>B61745</t>
+  </si>
+  <si>
+    <t>LANCER VIGILANCIA E SEGURANÇA</t>
+  </si>
+  <si>
+    <t>EP1285416</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212243500434</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535293PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:43:50.113</t>
+  </si>
+  <si>
+    <t>7530.59</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;10/07/2026b</t>
+  </si>
+  <si>
+    <t>Fora do mês vigente</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212244270436</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535295PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:44:27.337</t>
+  </si>
+  <si>
+    <t>980.70</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212246410444</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535303PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:46:41.65</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;06/08/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212247000445</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535304PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:47:00.58</t>
+  </si>
+  <si>
+    <t>479.00</t>
+  </si>
+  <si>
+    <t>02633186000141&amp;05/11/2026</t>
+  </si>
+  <si>
+    <t>07.10</t>
+  </si>
+  <si>
+    <t>B61746</t>
+  </si>
+  <si>
+    <t>LANCER SERVIÇOS GERAIS LTDA</t>
+  </si>
+  <si>
+    <t>EP1265302</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212348120446</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535305PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 23:48:12.143</t>
+  </si>
+  <si>
+    <t>10855.08</t>
+  </si>
+  <si>
+    <t>02633186000141&amp;16/11/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212241540427</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535286PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:41:54.807</t>
+  </si>
+  <si>
+    <t>45178.04</t>
+  </si>
+  <si>
+    <t>02633186000141&amp;09/08/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212242130428</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535287PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:42:13.51</t>
+  </si>
+  <si>
+    <t>8158.14</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;16/10/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212242320429</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535288PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:42:32.343</t>
+  </si>
+  <si>
+    <t>12990.34</t>
+  </si>
+  <si>
+    <t>EP1742502</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212242500430</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535289PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:42:50.797</t>
+  </si>
+  <si>
+    <t>10668.34</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;10/07/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212243090431</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535290PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:43:09.433</t>
+  </si>
+  <si>
+    <t>6903.05</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;16/11/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212243120432</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535291PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:43:12.957</t>
+  </si>
+  <si>
+    <t>62539.33</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212244450437</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535296PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:44:46.057</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212245040438</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535297PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:45:04.96</t>
+  </si>
+  <si>
+    <t>25972.33</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;07/07/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212245230439</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535298PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:45:23.493</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212245420440</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535299PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:45:42.173</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212245450441</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535300PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:45:45.717</t>
+  </si>
+  <si>
+    <t>40712.68</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212246040442</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535301PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:46:04.557</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608212246220443</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535302PO</t>
+  </si>
+  <si>
+    <t>2026-08-21 22:46:23.087</t>
+  </si>
+  <si>
+    <t>7827.92</t>
+  </si>
+  <si>
+    <t>02633186000141&amp;10/07/2026</t>
   </si>
 </sst>
 </file>
@@ -692,6 +1220,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1073,16 +1605,16 @@
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>13</v>
@@ -1097,24 +1629,24 @@
         <v>16</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
@@ -1129,48 +1661,48 @@
         <v>45544.78</v>
       </c>
       <c r="K2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
       </c>
       <c r="O2" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="P2" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="Q2" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="R2" t="s">
         <v>20</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="U2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
@@ -1185,51 +1717,51 @@
         <v>6130</v>
       </c>
       <c r="K3" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="L3" t="s">
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="O3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="P3" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="Q3" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="R3" t="s">
         <v>20</v>
       </c>
       <c r="S3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T3" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="U3" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
@@ -1244,258 +1776,261 @@
         <v>36939.5</v>
       </c>
       <c r="K4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="L4" t="s">
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="N4">
         <v>1</v>
       </c>
       <c r="O4" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="P4" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="Q4" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="R4" t="s">
         <v>20</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T4" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="U4" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
       </c>
       <c r="H5">
-        <v>254739</v>
+        <v>13371</v>
       </c>
       <c r="I5" s="1">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="J5">
-        <v>2983.75</v>
+        <v>17900</v>
       </c>
       <c r="K5" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="L5" t="s">
         <v>19</v>
       </c>
+      <c r="M5" t="s">
+        <v>114</v>
+      </c>
       <c r="O5" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="P5" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="Q5" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T5" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="U5" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="G6" t="s">
         <v>18</v>
       </c>
       <c r="H6">
-        <v>13371</v>
+        <v>95900</v>
       </c>
       <c r="I6" s="1">
         <v>46245</v>
       </c>
       <c r="J6">
-        <v>17900</v>
+        <v>4950</v>
       </c>
       <c r="K6" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="L6" t="s">
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="O6" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="P6" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="Q6" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="R6" t="s">
         <v>20</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T6" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="U6" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
         <v>18</v>
       </c>
       <c r="H7">
-        <v>95900</v>
+        <v>32739</v>
       </c>
       <c r="I7" s="1">
-        <v>46245</v>
+        <v>46150</v>
       </c>
       <c r="J7">
-        <v>4950</v>
+        <v>4961.32</v>
       </c>
       <c r="K7" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="O7" t="s">
-        <v>167</v>
+        <v>26</v>
       </c>
       <c r="P7" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="Q7" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="R7" t="s">
         <v>20</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T7" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="U7" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
         <v>18</v>
       </c>
       <c r="H8">
-        <v>32739</v>
+        <v>22890</v>
       </c>
       <c r="I8" s="1">
-        <v>46150</v>
+        <v>46204</v>
       </c>
       <c r="J8">
-        <v>4961.32</v>
+        <v>17036.599999999999</v>
       </c>
       <c r="K8" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L8" t="s">
         <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O8" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="P8" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="Q8" t="s">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="R8" t="s">
         <v>20</v>
@@ -1504,234 +2039,234 @@
         <v>43</v>
       </c>
       <c r="T8" t="s">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="U8" t="s">
-        <v>174</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>253</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>254</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>255</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>256</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="I9" s="1">
-        <v>46203</v>
+        <v>46220</v>
       </c>
       <c r="J9">
-        <v>660</v>
+        <v>12424</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>257</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="O9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="P9" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="Q9" t="s">
-        <v>64</v>
+        <v>258</v>
       </c>
       <c r="R9" t="s">
         <v>20</v>
       </c>
       <c r="S9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T9" t="s">
-        <v>175</v>
+        <v>59</v>
       </c>
       <c r="U9" t="s">
-        <v>160</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>197</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>199</v>
       </c>
       <c r="G10" t="s">
         <v>18</v>
       </c>
       <c r="H10">
-        <v>22890</v>
+        <v>21</v>
       </c>
       <c r="I10" s="1">
-        <v>46204</v>
+        <v>46238</v>
       </c>
       <c r="J10">
-        <v>17036.599999999999</v>
+        <v>100382</v>
       </c>
       <c r="K10" t="s">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="L10" t="s">
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="O10" t="s">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="P10" t="s">
-        <v>91</v>
+        <v>203</v>
       </c>
       <c r="Q10" t="s">
-        <v>37</v>
+        <v>204</v>
       </c>
       <c r="R10" t="s">
         <v>20</v>
       </c>
       <c r="S10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T10" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="U10" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="G11" t="s">
         <v>18</v>
       </c>
       <c r="H11">
-        <v>1475</v>
+        <v>159</v>
       </c>
       <c r="I11" s="1">
-        <v>46224</v>
+        <v>46238</v>
       </c>
       <c r="J11">
-        <v>15233.36</v>
+        <v>19309.14</v>
       </c>
       <c r="K11" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="L11" t="s">
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="O11" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="P11" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="Q11" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="R11" t="s">
         <v>20</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T11" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="U11" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="G12" t="s">
         <v>18</v>
       </c>
       <c r="H12">
-        <v>1456</v>
+        <v>29090</v>
       </c>
       <c r="I12" s="1">
-        <v>46205</v>
+        <v>46174</v>
       </c>
       <c r="J12">
-        <v>15233.36</v>
+        <v>588.6</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="L12" t="s">
         <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="O12" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
       <c r="P12" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="R12" t="s">
         <v>20</v>
@@ -1740,57 +2275,57 @@
         <v>43</v>
       </c>
       <c r="T12" t="s">
-        <v>29</v>
+        <v>118</v>
       </c>
       <c r="U12" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>178</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>179</v>
+        <v>49</v>
       </c>
       <c r="G13" t="s">
         <v>18</v>
       </c>
       <c r="H13">
-        <v>21</v>
+        <v>36993</v>
       </c>
       <c r="I13" s="1">
-        <v>46238</v>
+        <v>46204</v>
       </c>
       <c r="J13">
-        <v>100382</v>
+        <v>1300</v>
       </c>
       <c r="K13" t="s">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="L13" t="s">
         <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>181</v>
+        <v>57</v>
       </c>
       <c r="O13" t="s">
-        <v>182</v>
+        <v>51</v>
       </c>
       <c r="P13" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="Q13" t="s">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="R13" t="s">
         <v>20</v>
@@ -1799,452 +2334,2007 @@
         <v>43</v>
       </c>
       <c r="T13" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="U13" t="s">
-        <v>69</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
         <v>18</v>
       </c>
       <c r="H14">
-        <v>159</v>
+        <v>452</v>
       </c>
       <c r="I14" s="1">
-        <v>46238</v>
+        <v>46027</v>
       </c>
       <c r="J14">
-        <v>19309.14</v>
+        <v>138055</v>
       </c>
       <c r="K14" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="L14" t="s">
         <v>19</v>
       </c>
       <c r="M14" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="O14" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="P14" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="Q14" t="s">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="R14" t="s">
         <v>20</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T14" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="U14" t="s">
-        <v>160</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
       </c>
       <c r="H15">
-        <v>29090</v>
+        <v>1267</v>
       </c>
       <c r="I15" s="1">
-        <v>46174</v>
+        <v>45957</v>
       </c>
       <c r="J15">
-        <v>588.6</v>
+        <v>13243.82</v>
       </c>
       <c r="K15" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="L15" t="s">
         <v>19</v>
       </c>
-      <c r="M15" t="s">
-        <v>56</v>
-      </c>
-      <c r="O15" t="s">
-        <v>127</v>
+      <c r="O15">
+        <v>22688889000384</v>
       </c>
       <c r="P15" t="s">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="Q15" t="s">
-        <v>129</v>
+        <v>205</v>
       </c>
       <c r="R15" t="s">
         <v>20</v>
       </c>
       <c r="S15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T15" t="s">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="U15" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>261</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>262</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>263</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>133</v>
+        <v>264</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
       </c>
       <c r="H16">
-        <v>7900</v>
+        <v>210</v>
       </c>
       <c r="I16" s="1">
-        <v>46238</v>
+        <v>46248</v>
       </c>
       <c r="J16">
-        <v>2123.06</v>
+        <v>4680</v>
       </c>
       <c r="K16" t="s">
-        <v>134</v>
+        <v>265</v>
       </c>
       <c r="L16" t="s">
         <v>19</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
+        <v>242</v>
       </c>
       <c r="O16" t="s">
-        <v>135</v>
+        <v>266</v>
       </c>
       <c r="P16" t="s">
-        <v>136</v>
+        <v>267</v>
       </c>
       <c r="Q16" t="s">
-        <v>137</v>
+        <v>268</v>
       </c>
       <c r="R16" t="s">
         <v>20</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T16" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="U16" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" t="s">
         <v>139</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>140</v>
-      </c>
-      <c r="C17" t="s">
-        <v>141</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
       </c>
       <c r="E17" t="s">
+        <v>141</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17">
+        <v>35007</v>
+      </c>
+      <c r="I17" s="1">
+        <v>46220</v>
+      </c>
+      <c r="J17">
+        <v>57773.02</v>
+      </c>
+      <c r="K17" t="s">
         <v>142</v>
-      </c>
-      <c r="G17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H17">
-        <v>7898</v>
-      </c>
-      <c r="I17" s="1">
-        <v>46238</v>
-      </c>
-      <c r="J17">
-        <v>2461.98</v>
-      </c>
-      <c r="K17" t="s">
-        <v>134</v>
       </c>
       <c r="L17" t="s">
         <v>19</v>
       </c>
       <c r="M17" t="s">
-        <v>68</v>
+        <v>143</v>
       </c>
       <c r="O17" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="P17" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="Q17" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="R17" t="s">
         <v>20</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T17" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="U17" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>159</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>161</v>
       </c>
       <c r="G18" t="s">
         <v>18</v>
       </c>
       <c r="H18">
-        <v>36993</v>
+        <v>13428</v>
       </c>
       <c r="I18" s="1">
-        <v>46204</v>
+        <v>46246</v>
       </c>
       <c r="J18">
-        <v>1300</v>
+        <v>3500</v>
       </c>
       <c r="K18" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="L18" t="s">
         <v>19</v>
       </c>
       <c r="M18" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="O18" t="s">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="P18" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="Q18" t="s">
-        <v>51</v>
+        <v>165</v>
       </c>
       <c r="R18" t="s">
         <v>20</v>
       </c>
       <c r="S18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T18" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="U18" t="s">
-        <v>160</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>185</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="C19" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
       </c>
-      <c r="H19" t="s">
-        <v>189</v>
+      <c r="H19">
+        <v>1138</v>
       </c>
       <c r="I19" s="1">
-        <v>46223</v>
+        <v>46253</v>
       </c>
       <c r="J19">
-        <v>39987.660000000003</v>
+        <v>2431.64</v>
       </c>
       <c r="K19" t="s">
-        <v>190</v>
+        <v>219</v>
       </c>
       <c r="L19" t="s">
         <v>19</v>
       </c>
       <c r="M19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O19" t="s">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="P19" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="Q19" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="R19" t="s">
         <v>20</v>
       </c>
       <c r="S19" t="s">
+        <v>44</v>
+      </c>
+      <c r="T19" t="s">
+        <v>221</v>
+      </c>
+      <c r="U19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20">
+        <v>76555</v>
+      </c>
+      <c r="I20" s="1">
+        <v>46253</v>
+      </c>
+      <c r="J20">
+        <v>429.79</v>
+      </c>
+      <c r="K20" t="s">
+        <v>210</v>
+      </c>
+      <c r="L20" t="s">
+        <v>19</v>
+      </c>
+      <c r="O20" t="s">
+        <v>211</v>
+      </c>
+      <c r="P20" t="s">
+        <v>212</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>213</v>
+      </c>
+      <c r="R20" t="s">
+        <v>20</v>
+      </c>
+      <c r="S20" t="s">
+        <v>44</v>
+      </c>
+      <c r="T20" t="s">
+        <v>214</v>
+      </c>
+      <c r="U20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21">
+        <v>73150</v>
+      </c>
+      <c r="I21" s="1">
+        <v>46211</v>
+      </c>
+      <c r="J21">
+        <v>31736.080000000002</v>
+      </c>
+      <c r="K21" t="s">
+        <v>77</v>
+      </c>
+      <c r="L21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" t="s">
+        <v>78</v>
+      </c>
+      <c r="O21" t="s">
+        <v>79</v>
+      </c>
+      <c r="P21" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>80</v>
+      </c>
+      <c r="R21" t="s">
+        <v>20</v>
+      </c>
+      <c r="S21" t="s">
+        <v>44</v>
+      </c>
+      <c r="T21" t="s">
+        <v>81</v>
+      </c>
+      <c r="U21" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>222</v>
+      </c>
+      <c r="B22" t="s">
+        <v>223</v>
+      </c>
+      <c r="C22" t="s">
+        <v>224</v>
+      </c>
+      <c r="D22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>225</v>
+      </c>
+      <c r="G22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22">
+        <v>1730217184</v>
+      </c>
+      <c r="I22" s="1">
+        <v>46211</v>
+      </c>
+      <c r="J22">
+        <v>31736.080000000002</v>
+      </c>
+      <c r="K22" t="s">
+        <v>226</v>
+      </c>
+      <c r="L22" t="s">
+        <v>19</v>
+      </c>
+      <c r="O22" t="s">
+        <v>227</v>
+      </c>
+      <c r="P22" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>228</v>
+      </c>
+      <c r="R22" t="s">
+        <v>20</v>
+      </c>
+      <c r="S22" t="s">
         <v>43</v>
       </c>
-      <c r="T19" t="s">
-        <v>78</v>
-      </c>
-      <c r="U19" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I22" s="1"/>
+      <c r="T22" t="s">
+        <v>81</v>
+      </c>
+      <c r="U22" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I23" s="1"/>
+      <c r="A23" t="s">
+        <v>270</v>
+      </c>
+      <c r="B23" t="s">
+        <v>271</v>
+      </c>
+      <c r="C23" t="s">
+        <v>272</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s">
+        <v>273</v>
+      </c>
+      <c r="G23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23">
+        <v>31329</v>
+      </c>
+      <c r="I23" s="1">
+        <v>46253</v>
+      </c>
+      <c r="J23">
+        <v>4638.72</v>
+      </c>
+      <c r="K23" t="s">
+        <v>274</v>
+      </c>
+      <c r="L23" t="s">
+        <v>19</v>
+      </c>
+      <c r="O23" t="s">
+        <v>275</v>
+      </c>
+      <c r="P23" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>277</v>
+      </c>
+      <c r="R23" t="s">
+        <v>20</v>
+      </c>
+      <c r="S23" t="s">
+        <v>44</v>
+      </c>
+      <c r="T23" t="s">
+        <v>278</v>
+      </c>
+      <c r="U23" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I24" s="1"/>
+      <c r="A24" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" t="s">
+        <v>231</v>
+      </c>
+      <c r="D24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24">
+        <v>2409</v>
+      </c>
+      <c r="I24" s="1">
+        <v>46253</v>
+      </c>
+      <c r="J24">
+        <v>51240</v>
+      </c>
+      <c r="K24" t="s">
+        <v>233</v>
+      </c>
+      <c r="L24" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" t="s">
+        <v>58</v>
+      </c>
+      <c r="O24" t="s">
+        <v>234</v>
+      </c>
+      <c r="P24" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>236</v>
+      </c>
+      <c r="R24" t="s">
+        <v>20</v>
+      </c>
+      <c r="S24" t="s">
+        <v>44</v>
+      </c>
+      <c r="T24" t="s">
+        <v>100</v>
+      </c>
+      <c r="U24" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I25" s="1"/>
+      <c r="A25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" t="s">
+        <v>238</v>
+      </c>
+      <c r="C25" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
+        <v>240</v>
+      </c>
+      <c r="G25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25">
+        <v>2408</v>
+      </c>
+      <c r="I25" s="1">
+        <v>46253</v>
+      </c>
+      <c r="J25">
+        <v>54600</v>
+      </c>
+      <c r="K25" t="s">
+        <v>241</v>
+      </c>
+      <c r="L25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M25" t="s">
+        <v>58</v>
+      </c>
+      <c r="O25" t="s">
+        <v>234</v>
+      </c>
+      <c r="P25" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>236</v>
+      </c>
+      <c r="R25" t="s">
+        <v>20</v>
+      </c>
+      <c r="S25" t="s">
+        <v>44</v>
+      </c>
+      <c r="T25" t="s">
+        <v>100</v>
+      </c>
+      <c r="U25" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I26" s="1"/>
+      <c r="A26" t="s">
+        <v>243</v>
+      </c>
+      <c r="B26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C26" t="s">
+        <v>245</v>
+      </c>
+      <c r="D26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>246</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26">
+        <v>245</v>
+      </c>
+      <c r="I26" s="1">
+        <v>46253</v>
+      </c>
+      <c r="J26">
+        <v>23760</v>
+      </c>
+      <c r="K26" t="s">
+        <v>247</v>
+      </c>
+      <c r="L26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" t="s">
+        <v>248</v>
+      </c>
+      <c r="O26" t="s">
+        <v>249</v>
+      </c>
+      <c r="P26" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>251</v>
+      </c>
+      <c r="R26" t="s">
+        <v>20</v>
+      </c>
+      <c r="S26" t="s">
+        <v>44</v>
+      </c>
+      <c r="T26" t="s">
+        <v>65</v>
+      </c>
+      <c r="U26" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I27" s="1"/>
+      <c r="A27" t="s">
+        <v>279</v>
+      </c>
+      <c r="B27" t="s">
+        <v>280</v>
+      </c>
+      <c r="C27" t="s">
+        <v>281</v>
+      </c>
+      <c r="D27" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>282</v>
+      </c>
+      <c r="G27" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27">
+        <v>15372</v>
+      </c>
+      <c r="I27" s="1">
+        <v>46241</v>
+      </c>
+      <c r="J27">
+        <v>105122.59</v>
+      </c>
+      <c r="K27" t="s">
+        <v>283</v>
+      </c>
+      <c r="L27" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" t="s">
+        <v>284</v>
+      </c>
+      <c r="O27" t="s">
+        <v>285</v>
+      </c>
+      <c r="P27" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>287</v>
+      </c>
+      <c r="R27" t="s">
+        <v>20</v>
+      </c>
+      <c r="S27" t="s">
+        <v>44</v>
+      </c>
+      <c r="T27" t="s">
+        <v>221</v>
+      </c>
+      <c r="U27" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I28" s="1"/>
+      <c r="A28" t="s">
+        <v>288</v>
+      </c>
+      <c r="B28" t="s">
+        <v>289</v>
+      </c>
+      <c r="C28" t="s">
+        <v>290</v>
+      </c>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>291</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28">
+        <v>15262</v>
+      </c>
+      <c r="I28" s="1">
+        <v>46153</v>
+      </c>
+      <c r="J28">
+        <v>9372.24</v>
+      </c>
+      <c r="K28" t="s">
+        <v>292</v>
+      </c>
+      <c r="L28" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" t="s">
+        <v>284</v>
+      </c>
+      <c r="O28" t="s">
+        <v>285</v>
+      </c>
+      <c r="P28" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>287</v>
+      </c>
+      <c r="R28" t="s">
+        <v>20</v>
+      </c>
+      <c r="S28" t="s">
+        <v>44</v>
+      </c>
+      <c r="T28" t="s">
+        <v>221</v>
+      </c>
+      <c r="U28" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I29" s="1"/>
+      <c r="A29" t="s">
+        <v>294</v>
+      </c>
+      <c r="B29" t="s">
+        <v>295</v>
+      </c>
+      <c r="C29" t="s">
+        <v>296</v>
+      </c>
+      <c r="D29" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>297</v>
+      </c>
+      <c r="G29" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29">
+        <v>15371</v>
+      </c>
+      <c r="I29" s="1">
+        <v>46241</v>
+      </c>
+      <c r="J29">
+        <v>1073.56</v>
+      </c>
+      <c r="K29" t="s">
+        <v>283</v>
+      </c>
+      <c r="L29" t="s">
+        <v>19</v>
+      </c>
+      <c r="M29" t="s">
+        <v>284</v>
+      </c>
+      <c r="O29" t="s">
+        <v>285</v>
+      </c>
+      <c r="P29" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>287</v>
+      </c>
+      <c r="R29" t="s">
+        <v>20</v>
+      </c>
+      <c r="S29" t="s">
+        <v>44</v>
+      </c>
+      <c r="T29" t="s">
+        <v>221</v>
+      </c>
+      <c r="U29" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I30" s="1"/>
+      <c r="A30" t="s">
+        <v>298</v>
+      </c>
+      <c r="B30" t="s">
+        <v>299</v>
+      </c>
+      <c r="C30" t="s">
+        <v>300</v>
+      </c>
+      <c r="D30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" t="s">
+        <v>297</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30">
+        <v>15257</v>
+      </c>
+      <c r="I30" s="1">
+        <v>46150</v>
+      </c>
+      <c r="J30">
+        <v>1073.56</v>
+      </c>
+      <c r="K30" t="s">
+        <v>301</v>
+      </c>
+      <c r="L30" t="s">
+        <v>19</v>
+      </c>
+      <c r="M30" t="s">
+        <v>284</v>
+      </c>
+      <c r="O30" t="s">
+        <v>285</v>
+      </c>
+      <c r="P30" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>287</v>
+      </c>
+      <c r="R30" t="s">
+        <v>20</v>
+      </c>
+      <c r="S30" t="s">
+        <v>44</v>
+      </c>
+      <c r="T30" t="s">
+        <v>221</v>
+      </c>
+      <c r="U30" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I31" s="1"/>
+      <c r="A31" t="s">
+        <v>302</v>
+      </c>
+      <c r="B31" t="s">
+        <v>303</v>
+      </c>
+      <c r="C31" t="s">
+        <v>304</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>305</v>
+      </c>
+      <c r="G31" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31">
+        <v>27421</v>
+      </c>
+      <c r="I31" s="1">
+        <v>46241</v>
+      </c>
+      <c r="J31">
+        <v>603.65</v>
+      </c>
+      <c r="K31" t="s">
+        <v>306</v>
+      </c>
+      <c r="L31" t="s">
+        <v>19</v>
+      </c>
+      <c r="M31" t="s">
+        <v>307</v>
+      </c>
+      <c r="O31" t="s">
+        <v>308</v>
+      </c>
+      <c r="P31" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>310</v>
+      </c>
+      <c r="R31" t="s">
+        <v>20</v>
+      </c>
+      <c r="S31" t="s">
+        <v>44</v>
+      </c>
+      <c r="T31" t="s">
+        <v>221</v>
+      </c>
+      <c r="U31" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I32" s="1"/>
-    </row>
-    <row r="33" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I36" s="1"/>
-      <c r="M36" s="3"/>
-    </row>
-    <row r="37" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I46" s="1"/>
-    </row>
-    <row r="47" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" spans="9:13" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>311</v>
+      </c>
+      <c r="B32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>314</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32">
+        <v>27475</v>
+      </c>
+      <c r="I32" s="1">
+        <v>46251</v>
+      </c>
+      <c r="J32">
+        <v>13680</v>
+      </c>
+      <c r="K32" t="s">
+        <v>315</v>
+      </c>
+      <c r="L32" t="s">
+        <v>19</v>
+      </c>
+      <c r="M32" t="s">
+        <v>307</v>
+      </c>
+      <c r="O32" t="s">
+        <v>308</v>
+      </c>
+      <c r="P32" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>310</v>
+      </c>
+      <c r="R32" t="s">
+        <v>20</v>
+      </c>
+      <c r="S32" t="s">
+        <v>44</v>
+      </c>
+      <c r="T32" t="s">
+        <v>221</v>
+      </c>
+      <c r="U32" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>316</v>
+      </c>
+      <c r="B33" t="s">
+        <v>317</v>
+      </c>
+      <c r="C33" t="s">
+        <v>318</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>319</v>
+      </c>
+      <c r="G33" t="s">
+        <v>18</v>
+      </c>
+      <c r="H33">
+        <v>27047</v>
+      </c>
+      <c r="I33" s="1">
+        <v>46153</v>
+      </c>
+      <c r="J33">
+        <v>56935.15</v>
+      </c>
+      <c r="K33" t="s">
+        <v>320</v>
+      </c>
+      <c r="L33" t="s">
+        <v>19</v>
+      </c>
+      <c r="M33" t="s">
+        <v>284</v>
+      </c>
+      <c r="O33" t="s">
+        <v>308</v>
+      </c>
+      <c r="P33" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>310</v>
+      </c>
+      <c r="R33" t="s">
+        <v>20</v>
+      </c>
+      <c r="S33" t="s">
+        <v>44</v>
+      </c>
+      <c r="T33" t="s">
+        <v>221</v>
+      </c>
+      <c r="U33" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>321</v>
+      </c>
+      <c r="B34" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" t="s">
+        <v>323</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" t="s">
+        <v>324</v>
+      </c>
+      <c r="G34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34">
+        <v>15384</v>
+      </c>
+      <c r="I34" s="1">
+        <v>46251</v>
+      </c>
+      <c r="J34">
+        <v>10153.26</v>
+      </c>
+      <c r="K34" t="s">
+        <v>325</v>
+      </c>
+      <c r="L34" t="s">
+        <v>19</v>
+      </c>
+      <c r="M34" t="s">
+        <v>284</v>
+      </c>
+      <c r="O34" t="s">
+        <v>285</v>
+      </c>
+      <c r="P34" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>287</v>
+      </c>
+      <c r="R34" t="s">
+        <v>20</v>
+      </c>
+      <c r="S34" t="s">
+        <v>44</v>
+      </c>
+      <c r="T34" t="s">
+        <v>221</v>
+      </c>
+      <c r="U34" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" t="s">
+        <v>327</v>
+      </c>
+      <c r="C35" t="s">
+        <v>328</v>
+      </c>
+      <c r="D35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" t="s">
+        <v>329</v>
+      </c>
+      <c r="G35" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35">
+        <v>15369</v>
+      </c>
+      <c r="I35" s="1">
+        <v>46241</v>
+      </c>
+      <c r="J35">
+        <v>16167.19</v>
+      </c>
+      <c r="K35" t="s">
+        <v>283</v>
+      </c>
+      <c r="L35" t="s">
+        <v>19</v>
+      </c>
+      <c r="M35" t="s">
+        <v>284</v>
+      </c>
+      <c r="O35" t="s">
+        <v>285</v>
+      </c>
+      <c r="P35" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>330</v>
+      </c>
+      <c r="R35" t="s">
+        <v>20</v>
+      </c>
+      <c r="S35" t="s">
+        <v>44</v>
+      </c>
+      <c r="T35" t="s">
+        <v>221</v>
+      </c>
+      <c r="U35" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" t="s">
+        <v>332</v>
+      </c>
+      <c r="C36" t="s">
+        <v>333</v>
+      </c>
+      <c r="D36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s">
+        <v>334</v>
+      </c>
+      <c r="G36" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36">
+        <v>15263</v>
+      </c>
+      <c r="I36" s="1">
+        <v>46153</v>
+      </c>
+      <c r="J36">
+        <v>13277.34</v>
+      </c>
+      <c r="K36" t="s">
+        <v>335</v>
+      </c>
+      <c r="L36" t="s">
+        <v>19</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="O36" t="s">
+        <v>285</v>
+      </c>
+      <c r="P36" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>287</v>
+      </c>
+      <c r="R36" t="s">
+        <v>20</v>
+      </c>
+      <c r="S36" t="s">
+        <v>44</v>
+      </c>
+      <c r="T36" t="s">
+        <v>221</v>
+      </c>
+      <c r="U36" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>336</v>
+      </c>
+      <c r="B37" t="s">
+        <v>337</v>
+      </c>
+      <c r="C37" t="s">
+        <v>338</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" t="s">
+        <v>339</v>
+      </c>
+      <c r="G37" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37">
+        <v>15385</v>
+      </c>
+      <c r="I37" s="1">
+        <v>46251</v>
+      </c>
+      <c r="J37">
+        <v>8591.2199999999993</v>
+      </c>
+      <c r="K37" t="s">
+        <v>340</v>
+      </c>
+      <c r="L37" t="s">
+        <v>19</v>
+      </c>
+      <c r="M37" t="s">
+        <v>284</v>
+      </c>
+      <c r="O37" t="s">
+        <v>285</v>
+      </c>
+      <c r="P37" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>287</v>
+      </c>
+      <c r="R37" t="s">
+        <v>20</v>
+      </c>
+      <c r="S37" t="s">
+        <v>44</v>
+      </c>
+      <c r="T37" t="s">
+        <v>221</v>
+      </c>
+      <c r="U37" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>341</v>
+      </c>
+      <c r="B38" t="s">
+        <v>342</v>
+      </c>
+      <c r="C38" t="s">
+        <v>343</v>
+      </c>
+      <c r="D38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" t="s">
+        <v>344</v>
+      </c>
+      <c r="G38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38">
+        <v>15370</v>
+      </c>
+      <c r="I38" s="1">
+        <v>46241</v>
+      </c>
+      <c r="J38">
+        <v>77833.64</v>
+      </c>
+      <c r="K38" t="s">
+        <v>283</v>
+      </c>
+      <c r="L38" t="s">
+        <v>19</v>
+      </c>
+      <c r="M38" t="s">
+        <v>284</v>
+      </c>
+      <c r="O38" t="s">
+        <v>285</v>
+      </c>
+      <c r="P38" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>287</v>
+      </c>
+      <c r="R38" t="s">
+        <v>20</v>
+      </c>
+      <c r="S38" t="s">
+        <v>44</v>
+      </c>
+      <c r="T38" t="s">
+        <v>221</v>
+      </c>
+      <c r="U38" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>345</v>
+      </c>
+      <c r="B39" t="s">
+        <v>346</v>
+      </c>
+      <c r="C39" t="s">
+        <v>347</v>
+      </c>
+      <c r="D39" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39" t="s">
+        <v>282</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39">
+        <v>15258</v>
+      </c>
+      <c r="I39" s="1">
+        <v>46150</v>
+      </c>
+      <c r="J39">
+        <v>105122.59</v>
+      </c>
+      <c r="K39" t="s">
+        <v>301</v>
+      </c>
+      <c r="L39" t="s">
+        <v>19</v>
+      </c>
+      <c r="M39" t="s">
+        <v>284</v>
+      </c>
+      <c r="O39" t="s">
+        <v>285</v>
+      </c>
+      <c r="P39" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>287</v>
+      </c>
+      <c r="R39" t="s">
+        <v>20</v>
+      </c>
+      <c r="S39" t="s">
+        <v>44</v>
+      </c>
+      <c r="T39" t="s">
+        <v>221</v>
+      </c>
+      <c r="U39" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>348</v>
+      </c>
+      <c r="B40" t="s">
+        <v>349</v>
+      </c>
+      <c r="C40" t="s">
+        <v>350</v>
+      </c>
+      <c r="D40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" t="s">
+        <v>351</v>
+      </c>
+      <c r="G40" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40">
+        <v>15259</v>
+      </c>
+      <c r="I40" s="1">
+        <v>46150</v>
+      </c>
+      <c r="J40">
+        <v>32324</v>
+      </c>
+      <c r="K40" t="s">
+        <v>352</v>
+      </c>
+      <c r="L40" t="s">
+        <v>19</v>
+      </c>
+      <c r="M40" t="s">
+        <v>284</v>
+      </c>
+      <c r="O40" t="s">
+        <v>285</v>
+      </c>
+      <c r="P40" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>287</v>
+      </c>
+      <c r="R40" t="s">
+        <v>20</v>
+      </c>
+      <c r="S40" t="s">
+        <v>44</v>
+      </c>
+      <c r="T40" t="s">
+        <v>221</v>
+      </c>
+      <c r="U40" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>353</v>
+      </c>
+      <c r="B41" t="s">
+        <v>354</v>
+      </c>
+      <c r="C41" t="s">
+        <v>355</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" t="s">
+        <v>324</v>
+      </c>
+      <c r="G41" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41">
+        <v>15260</v>
+      </c>
+      <c r="I41" s="1">
+        <v>46150</v>
+      </c>
+      <c r="J41">
+        <v>10153.26</v>
+      </c>
+      <c r="K41" t="s">
+        <v>352</v>
+      </c>
+      <c r="L41" t="s">
+        <v>19</v>
+      </c>
+      <c r="M41" t="s">
+        <v>284</v>
+      </c>
+      <c r="O41" t="s">
+        <v>285</v>
+      </c>
+      <c r="P41" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>287</v>
+      </c>
+      <c r="R41" t="s">
+        <v>20</v>
+      </c>
+      <c r="S41" t="s">
+        <v>44</v>
+      </c>
+      <c r="T41" t="s">
+        <v>221</v>
+      </c>
+      <c r="U41" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>356</v>
+      </c>
+      <c r="B42" t="s">
+        <v>357</v>
+      </c>
+      <c r="C42" t="s">
+        <v>358</v>
+      </c>
+      <c r="D42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" t="s">
+        <v>344</v>
+      </c>
+      <c r="G42" t="s">
+        <v>18</v>
+      </c>
+      <c r="H42">
+        <v>15256</v>
+      </c>
+      <c r="I42" s="1">
+        <v>46150</v>
+      </c>
+      <c r="J42">
+        <v>77833.64</v>
+      </c>
+      <c r="K42" t="s">
+        <v>301</v>
+      </c>
+      <c r="L42" t="s">
+        <v>19</v>
+      </c>
+      <c r="M42" t="s">
+        <v>284</v>
+      </c>
+      <c r="O42" t="s">
+        <v>285</v>
+      </c>
+      <c r="P42" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>287</v>
+      </c>
+      <c r="R42" t="s">
+        <v>20</v>
+      </c>
+      <c r="S42" t="s">
+        <v>44</v>
+      </c>
+      <c r="T42" t="s">
+        <v>221</v>
+      </c>
+      <c r="U42" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>359</v>
+      </c>
+      <c r="B43" t="s">
+        <v>360</v>
+      </c>
+      <c r="C43" t="s">
+        <v>361</v>
+      </c>
+      <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" t="s">
+        <v>362</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
+      </c>
+      <c r="H43">
+        <v>27422</v>
+      </c>
+      <c r="I43" s="1">
+        <v>46241</v>
+      </c>
+      <c r="J43">
+        <v>51307.73</v>
+      </c>
+      <c r="K43" t="s">
+        <v>306</v>
+      </c>
+      <c r="L43" t="s">
+        <v>19</v>
+      </c>
+      <c r="M43" t="s">
+        <v>307</v>
+      </c>
+      <c r="O43" t="s">
+        <v>308</v>
+      </c>
+      <c r="P43" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>310</v>
+      </c>
+      <c r="R43" t="s">
+        <v>20</v>
+      </c>
+      <c r="S43" t="s">
+        <v>44</v>
+      </c>
+      <c r="T43" t="s">
+        <v>221</v>
+      </c>
+      <c r="U43" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>363</v>
+      </c>
+      <c r="B44" t="s">
+        <v>364</v>
+      </c>
+      <c r="C44" t="s">
+        <v>365</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>305</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44">
+        <v>27474</v>
+      </c>
+      <c r="I44" s="1">
+        <v>46251</v>
+      </c>
+      <c r="J44">
+        <v>603.65</v>
+      </c>
+      <c r="K44" t="s">
+        <v>315</v>
+      </c>
+      <c r="L44" t="s">
+        <v>19</v>
+      </c>
+      <c r="M44" t="s">
+        <v>307</v>
+      </c>
+      <c r="O44" t="s">
+        <v>308</v>
+      </c>
+      <c r="P44" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>310</v>
+      </c>
+      <c r="R44" t="s">
+        <v>20</v>
+      </c>
+      <c r="S44" t="s">
+        <v>44</v>
+      </c>
+      <c r="T44" t="s">
+        <v>221</v>
+      </c>
+      <c r="U44" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>366</v>
+      </c>
+      <c r="B45" t="s">
+        <v>367</v>
+      </c>
+      <c r="C45" t="s">
+        <v>368</v>
+      </c>
+      <c r="D45" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" t="s">
+        <v>369</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45">
+        <v>27049</v>
+      </c>
+      <c r="I45" s="1">
+        <v>46153</v>
+      </c>
+      <c r="J45">
+        <v>9865.06</v>
+      </c>
+      <c r="K45" t="s">
+        <v>370</v>
+      </c>
+      <c r="L45" t="s">
+        <v>19</v>
+      </c>
+      <c r="M45" t="s">
+        <v>307</v>
+      </c>
+      <c r="O45" t="s">
+        <v>308</v>
+      </c>
+      <c r="P45" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>310</v>
+      </c>
+      <c r="R45" t="s">
+        <v>20</v>
+      </c>
+      <c r="S45" t="s">
+        <v>44</v>
+      </c>
+      <c r="T45" t="s">
+        <v>221</v>
+      </c>
+      <c r="U45" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" t="s">
+        <v>148</v>
+      </c>
+      <c r="C46" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" t="s">
+        <v>150</v>
+      </c>
+      <c r="G46" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" t="s">
+        <v>151</v>
+      </c>
+      <c r="I46" s="1">
+        <v>46237</v>
+      </c>
+      <c r="J46">
+        <v>14171.56</v>
+      </c>
+      <c r="K46" t="s">
+        <v>152</v>
+      </c>
+      <c r="L46" t="s">
+        <v>19</v>
+      </c>
+      <c r="M46" t="s">
+        <v>54</v>
+      </c>
+      <c r="O46" t="s">
+        <v>153</v>
+      </c>
+      <c r="P46" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>155</v>
+      </c>
+      <c r="R46" t="s">
+        <v>20</v>
+      </c>
+      <c r="S46" t="s">
+        <v>44</v>
+      </c>
+      <c r="T46" t="s">
+        <v>156</v>
+      </c>
+      <c r="U46" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" t="s">
+        <v>85</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47">
+        <v>111828</v>
+      </c>
+      <c r="I47" s="1">
+        <v>46237</v>
+      </c>
+      <c r="J47">
+        <v>710.73</v>
+      </c>
+      <c r="K47" t="s">
+        <v>86</v>
+      </c>
+      <c r="L47" t="s">
+        <v>19</v>
+      </c>
+      <c r="M47" t="s">
+        <v>56</v>
+      </c>
+      <c r="O47" t="s">
+        <v>87</v>
+      </c>
+      <c r="P47" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>88</v>
+      </c>
+      <c r="R47" t="s">
+        <v>20</v>
+      </c>
+      <c r="S47" t="s">
+        <v>44</v>
+      </c>
+      <c r="T47" t="s">
+        <v>62</v>
+      </c>
+      <c r="U47" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="I48" s="1"/>
     </row>
     <row r="49" spans="9:13" x14ac:dyDescent="0.35">

--- a/AUTOMOTIVO.xlsx
+++ b/AUTOMOTIVO.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemininar-my.sharepoint.com/personal/guilherme_deschamps_capgemini_com/Documents/Documents/INVOICE/DASHBOARD/AUTOMOTIVO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUDESCHA\Downloads\Dashaboard em HTML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{519F2E90-BF14-445A-9765-AB404186F25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0846D51-A337-4AF3-9397-D975265F6CDD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166550A9-E519-4145-8E22-BE50EC0CB25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39811114-C66D-43D9-8E26-15996D34E7BD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="460">
   <si>
     <t>ASV Ref Id</t>
   </si>
@@ -104,24 +104,6 @@
     <t>Internal Query</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202605081719380533</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85507069PO</t>
-  </si>
-  <si>
-    <t>2026-05-08 17:19:38.617</t>
-  </si>
-  <si>
-    <t>4961.32</t>
-  </si>
-  <si>
-    <t>61241279000190&amp;22/06/2026&amp;</t>
-  </si>
-  <si>
-    <t>B71378</t>
-  </si>
-  <si>
     <t>13243.82</t>
   </si>
   <si>
@@ -137,15 +119,6 @@
     <t>22688889000384&amp;25/11/2025&amp;</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202607011622160651</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85521254PO</t>
-  </si>
-  <si>
-    <t>2026-07-01 16:22:17.133</t>
-  </si>
-  <si>
     <t>17036.60</t>
   </si>
   <si>
@@ -158,9 +131,6 @@
     <t>EP1403647</t>
   </si>
   <si>
-    <t>Clemente Ledon</t>
-  </si>
-  <si>
     <t>Fornecedor</t>
   </si>
   <si>
@@ -221,12 +191,6 @@
     <t>Caroline Diniz Silva</t>
   </si>
   <si>
-    <t>14.10</t>
-  </si>
-  <si>
-    <t>B71364</t>
-  </si>
-  <si>
     <t>Mary Ellen Silva</t>
   </si>
   <si>
@@ -236,9 +200,6 @@
     <t>Arthur Castilho</t>
   </si>
   <si>
-    <t>Andre Bisetto</t>
-  </si>
-  <si>
     <t>Thalles Miranda</t>
   </si>
   <si>
@@ -344,18 +305,12 @@
     <t>Marinete Pereira</t>
   </si>
   <si>
-    <t>HURTH INFER IND. DE MAQ. E FER</t>
-  </si>
-  <si>
     <t>LOGCOMEX S/A</t>
   </si>
   <si>
     <t>POLGAS DISTRIBUIDORA DE GAS LT</t>
   </si>
   <si>
-    <t>LUCIANA R.C. LEITE MEI</t>
-  </si>
-  <si>
     <t>EKAIZEN GESTAO EMPRE DIGITAL L</t>
   </si>
   <si>
@@ -398,30 +353,6 @@
     <t>Everton Santos</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608121250060439</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85533014PO</t>
-  </si>
-  <si>
-    <t>2026-08-12 12:50:06.187</t>
-  </si>
-  <si>
-    <t>16915.50</t>
-  </si>
-  <si>
-    <t>45069283000166&amp;10/10/2026&amp;</t>
-  </si>
-  <si>
-    <t>B69170</t>
-  </si>
-  <si>
-    <t>MACEDO TRANSPORTES PESADOS LTD</t>
-  </si>
-  <si>
-    <t>EP6833</t>
-  </si>
-  <si>
     <t>SKFAUTOAPE202606011831380265</t>
   </si>
   <si>
@@ -539,54 +470,6 @@
     <t>EP12398</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608201946470375</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535007PO</t>
-  </si>
-  <si>
-    <t>2026-08-20 19:46:47.403</t>
-  </si>
-  <si>
-    <t>45544.78</t>
-  </si>
-  <si>
-    <t>35848024000180&amp;20/09/2026</t>
-  </si>
-  <si>
-    <t>B72947</t>
-  </si>
-  <si>
-    <t>CIBRATRADE MARKETING INTE LTDA</t>
-  </si>
-  <si>
-    <t>EP7765</t>
-  </si>
-  <si>
-    <t>Mauricio Valdivino</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608202125170388</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535042PO</t>
-  </si>
-  <si>
-    <t>2026-08-20 21:25:17.417</t>
-  </si>
-  <si>
-    <t>6130.00</t>
-  </si>
-  <si>
-    <t>14824170000103&amp;NA</t>
-  </si>
-  <si>
-    <t>EP13762</t>
-  </si>
-  <si>
-    <t>Pedido incorreto</t>
-  </si>
-  <si>
     <t>SKFAUTOAPE202608111944250344</t>
   </si>
   <si>
@@ -620,42 +503,12 @@
     <t>CNPJ Divergente do pedido</t>
   </si>
   <si>
-    <t>EP12315</t>
-  </si>
-  <si>
     <t>Alexssandro Silva</t>
   </si>
   <si>
     <t>Alterar código de mercadoria</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608041401390305</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85531125PO</t>
-  </si>
-  <si>
-    <t>2026-08-04 14:01:39.957</t>
-  </si>
-  <si>
-    <t>100382.00</t>
-  </si>
-  <si>
-    <t>12981051000120&amp;01/12/2026</t>
-  </si>
-  <si>
-    <t>14.06</t>
-  </si>
-  <si>
-    <t>B71390</t>
-  </si>
-  <si>
-    <t>IBRATECH AUTOMACAO LTDA</t>
-  </si>
-  <si>
-    <t>EP2067</t>
-  </si>
-  <si>
     <t>EP13503</t>
   </si>
   <si>
@@ -701,9 +554,6 @@
     <t>34151100002850&amp;NA</t>
   </si>
   <si>
-    <t>EP901064</t>
-  </si>
-  <si>
     <t>Vitor Goncalves</t>
   </si>
   <si>
@@ -770,129 +620,15 @@
     <t>17.01</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608201350240360</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85534977PO</t>
-  </si>
-  <si>
-    <t>2026-08-20 13:50:24.77</t>
-  </si>
-  <si>
-    <t>23760.00</t>
-  </si>
-  <si>
-    <t>20918745000141&amp;19/09/2026</t>
-  </si>
-  <si>
-    <t>03.05</t>
-  </si>
-  <si>
-    <t>B73272</t>
-  </si>
-  <si>
-    <t>FELIPE TEIXEIRA PIRES</t>
-  </si>
-  <si>
-    <t>EP13505</t>
-  </si>
-  <si>
     <t>Confirmar novo pedido</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202607171351260621</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85525659PO</t>
-  </si>
-  <si>
-    <t>2026-07-17 13:51:26.94</t>
-  </si>
-  <si>
-    <t>12424.00</t>
-  </si>
-  <si>
-    <t>14824170000103&amp;31/07/2026</t>
-  </si>
-  <si>
-    <t>EP6563</t>
-  </si>
-  <si>
-    <t>Ajustar pedido para amount</t>
-  </si>
-  <si>
-    <t>DHL EXPRESS</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608181859350157</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85534388PO</t>
-  </si>
-  <si>
-    <t>2026-08-18 18:59:35.983</t>
-  </si>
-  <si>
-    <t>4392.58</t>
-  </si>
-  <si>
-    <t>13182443000273&amp;NA</t>
-  </si>
-  <si>
-    <t>B69099</t>
-  </si>
-  <si>
-    <t>FASTENAL B</t>
-  </si>
-  <si>
-    <t>P120899</t>
-  </si>
-  <si>
     <t>DNV Business Assurance Avaliações e Certificações Brasil Ltda</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608191343120226</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85534588PO</t>
-  </si>
-  <si>
-    <t>2026-08-19 13:43:13.0</t>
-  </si>
-  <si>
-    <t>4638.72</t>
-  </si>
-  <si>
-    <t>06203366000144&amp;NA&amp;</t>
-  </si>
-  <si>
-    <t>B73218</t>
-  </si>
-  <si>
-    <t>LAVANDERIA ECOLOGY EIRELI</t>
-  </si>
-  <si>
-    <t>EP1696595</t>
-  </si>
-  <si>
-    <t>Luiz dos Santos</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212243310433</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535292PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:43:31.493</t>
-  </si>
-  <si>
     <t>84466.00</t>
   </si>
   <si>
-    <t>02633187000196&amp;05/11/2026</t>
-  </si>
-  <si>
     <t>11.02</t>
   </si>
   <si>
@@ -905,63 +641,12 @@
     <t>EP1285416</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608212243500434</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535293PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:43:50.113</t>
-  </si>
-  <si>
-    <t>7530.59</t>
-  </si>
-  <si>
-    <t>02633187000196&amp;10/07/2026b</t>
-  </si>
-  <si>
     <t>Fora do mês vigente</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608212244270436</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535295PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:44:27.337</t>
-  </si>
-  <si>
     <t>980.70</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608212246410444</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535303PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:46:41.65</t>
-  </si>
-  <si>
-    <t>02633187000196&amp;06/08/2026</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212247000445</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535304PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:47:00.58</t>
-  </si>
-  <si>
-    <t>479.00</t>
-  </si>
-  <si>
-    <t>02633186000141&amp;05/11/2026</t>
-  </si>
-  <si>
     <t>07.10</t>
   </si>
   <si>
@@ -974,184 +659,766 @@
     <t>EP1265302</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608212348120446</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535305PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 23:48:12.143</t>
-  </si>
-  <si>
-    <t>10855.08</t>
-  </si>
-  <si>
-    <t>02633186000141&amp;16/11/2026</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212241540427</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535286PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:41:54.807</t>
-  </si>
-  <si>
-    <t>45178.04</t>
-  </si>
-  <si>
     <t>02633186000141&amp;09/08/2026</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608212242130428</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535287PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:42:13.51</t>
-  </si>
-  <si>
-    <t>8158.14</t>
-  </si>
-  <si>
-    <t>02633187000196&amp;16/10/2026</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212242320429</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535288PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:42:32.343</t>
-  </si>
-  <si>
     <t>12990.34</t>
   </si>
   <si>
-    <t>EP1742502</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212242500430</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535289PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:42:50.797</t>
-  </si>
-  <si>
-    <t>10668.34</t>
-  </si>
-  <si>
-    <t>02633187000196&amp;10/07/2026</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212243090431</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535290PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:43:09.433</t>
-  </si>
-  <si>
-    <t>6903.05</t>
-  </si>
-  <si>
-    <t>02633187000196&amp;16/11/2026</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212243120432</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535291PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:43:12.957</t>
-  </si>
-  <si>
     <t>62539.33</t>
   </si>
   <si>
-    <t>SKFAUTOAPE202608212244450437</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535296PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:44:46.057</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212245040438</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535297PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:45:04.96</t>
-  </si>
-  <si>
-    <t>25972.33</t>
-  </si>
-  <si>
-    <t>02633187000196&amp;07/07/2026</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212245230439</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535298PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:45:23.493</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212245420440</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535299PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:45:42.173</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212245450441</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535300PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:45:45.717</t>
-  </si>
-  <si>
-    <t>40712.68</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212246040442</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535301PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:46:04.557</t>
-  </si>
-  <si>
-    <t>SKFAUTOAPE202608212246220443</t>
-  </si>
-  <si>
-    <t>EmailRefSKF9645L85535302PO</t>
-  </si>
-  <si>
-    <t>2026-08-21 22:46:23.087</t>
-  </si>
-  <si>
-    <t>7827.92</t>
-  </si>
-  <si>
-    <t>02633186000141&amp;10/07/2026</t>
+    <t>SKFAUTOAPE202608201947240377</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535009PO</t>
+  </si>
+  <si>
+    <t>2026-08-20 19:47:24.79</t>
+  </si>
+  <si>
+    <t>7890.17</t>
+  </si>
+  <si>
+    <t>53496907000150&amp;NA</t>
+  </si>
+  <si>
+    <t>B70621</t>
+  </si>
+  <si>
+    <t>APDATA DO BRASIL SOFTWARE LTDA</t>
+  </si>
+  <si>
+    <t>Informar pedido de compras</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609041347150606</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538739PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 13:47:15.993</t>
+  </si>
+  <si>
+    <t>4942.72</t>
+  </si>
+  <si>
+    <t>31861323000527&amp;01/10/2026</t>
+  </si>
+  <si>
+    <t>B73314</t>
+  </si>
+  <si>
+    <t>CULLIGAN BRASIL LTDA</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609041349530612</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538746PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 13:49:53.927</t>
+  </si>
+  <si>
+    <t>3190.41</t>
+  </si>
+  <si>
+    <t>08665722000177&amp;02/12/2026</t>
+  </si>
+  <si>
+    <t>B89171</t>
+  </si>
+  <si>
+    <t>VERSATRONIC CNC ELETRONICA LTD</t>
+  </si>
+  <si>
+    <t>EP14633</t>
+  </si>
+  <si>
+    <t>Rodrigo Silva</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609011516420301</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85537699PO</t>
+  </si>
+  <si>
+    <t>2026-09-01 15:16:42.28</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608311938570216</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85537383PO</t>
+  </si>
+  <si>
+    <t>2026-08-31 19:38:58.017</t>
+  </si>
+  <si>
+    <t>1162.95</t>
+  </si>
+  <si>
+    <t>58890252000113&amp;NA</t>
+  </si>
+  <si>
+    <t>B61031</t>
+  </si>
+  <si>
+    <t>DHL EXPRESS (BRASIL) LTDA</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032001220457</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538426PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:01:22.193</t>
+  </si>
+  <si>
+    <t>37500.00</t>
+  </si>
+  <si>
+    <t>05072682000161&amp;02/12/2026&amp;1001</t>
+  </si>
+  <si>
+    <t>B63822</t>
+  </si>
+  <si>
+    <t>USIDUR INDUSTRIA E COMERCI EIR</t>
+  </si>
+  <si>
+    <t>EP7395</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032003420466</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538435PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:03:42.123</t>
+  </si>
+  <si>
+    <t>6280.00</t>
+  </si>
+  <si>
+    <t>09339962000144&amp;NA</t>
+  </si>
+  <si>
+    <t>B68306</t>
+  </si>
+  <si>
+    <t>SILVINO VIANA DOS SANTOS ME</t>
+  </si>
+  <si>
+    <t>EP14586</t>
+  </si>
+  <si>
+    <t>Luis Eugenio</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032022050475</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538446PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:22:05.373</t>
+  </si>
+  <si>
+    <t>656.56</t>
+  </si>
+  <si>
+    <t>00973749000891&amp;04/11/2026</t>
+  </si>
+  <si>
+    <t>B71195</t>
+  </si>
+  <si>
+    <t>TOP SERVICE SERVICOS E SIS LTD</t>
+  </si>
+  <si>
+    <t>EP3360</t>
+  </si>
+  <si>
+    <t>Alterar pedido para amount</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032022240476</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538447PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:22:24.387</t>
+  </si>
+  <si>
+    <t>35254.01</t>
+  </si>
+  <si>
+    <t>EP1088685</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032023060479</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538450PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:23:06.43</t>
+  </si>
+  <si>
+    <t>36215.24</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608251902040642</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85535860PO</t>
+  </si>
+  <si>
+    <t>2026-08-25 19:02:04.27</t>
+  </si>
+  <si>
+    <t>572.10</t>
+  </si>
+  <si>
+    <t>12693949000101&amp;31/08/2026</t>
+  </si>
+  <si>
+    <t>b69960</t>
+  </si>
+  <si>
+    <t>MORATA G N S E M SOC DE ADVOGA</t>
+  </si>
+  <si>
+    <t>EP1784388</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608031947410234</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85530903PO</t>
+  </si>
+  <si>
+    <t>2026-08-03 19:47:42.053</t>
+  </si>
+  <si>
+    <t>15233.36</t>
+  </si>
+  <si>
+    <t>22688889000346&amp;01/09/2026</t>
+  </si>
+  <si>
+    <t>B72607</t>
+  </si>
+  <si>
+    <t>STYLUX BRASIL SIST DE ILU E EN</t>
+  </si>
+  <si>
+    <t>EP1725073</t>
+  </si>
+  <si>
+    <t>Evandro Rampazzo</t>
+  </si>
+  <si>
+    <t>22688889000384</t>
+  </si>
+  <si>
+    <t>Stylux Brasil Sistemas de Iluminação e Energia SA.</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609041618230623</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538816PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 16:18:23.547</t>
+  </si>
+  <si>
+    <t>9441.99</t>
+  </si>
+  <si>
+    <t>48763155000106&amp;NA</t>
+  </si>
+  <si>
+    <t>B71627</t>
+  </si>
+  <si>
+    <t>KUKA ROBOTER DO BRASIL</t>
+  </si>
+  <si>
+    <t>EP13710</t>
+  </si>
+  <si>
+    <t>Arthur Bicalho</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609041621180634</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538827PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 16:21:19.02</t>
+  </si>
+  <si>
+    <t>15700.00</t>
+  </si>
+  <si>
+    <t>08796736000120&amp;03/10/2026</t>
+  </si>
+  <si>
+    <t>14.02</t>
+  </si>
+  <si>
+    <t>B72223</t>
+  </si>
+  <si>
+    <t>IT - ELETRICA COM E SERVICOS</t>
+  </si>
+  <si>
+    <t>EP4978</t>
+  </si>
+  <si>
+    <t>Paulo Alves</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609012005060337</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85537826PO</t>
+  </si>
+  <si>
+    <t>2026-09-01 20:05:06.693</t>
+  </si>
+  <si>
+    <t>660.00</t>
+  </si>
+  <si>
+    <t>45662885000122&amp;NA&amp;9001</t>
+  </si>
+  <si>
+    <t>B72620</t>
+  </si>
+  <si>
+    <t>LEONARDO TAVARES DA SILVA DE O</t>
+  </si>
+  <si>
+    <t>EP14140</t>
+  </si>
+  <si>
+    <t>Ricardo Alves</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608132004130497</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85533491PO</t>
+  </si>
+  <si>
+    <t>2026-08-13 20:04:13.987</t>
+  </si>
+  <si>
+    <t>6617.30</t>
+  </si>
+  <si>
+    <t>04150123000160&amp;14/10/2026</t>
+  </si>
+  <si>
+    <t>B72702</t>
+  </si>
+  <si>
+    <t>CORSI - RENTAL LTDA</t>
+  </si>
+  <si>
+    <t>EP7465</t>
+  </si>
+  <si>
+    <t>Wiliam Granzoto</t>
+  </si>
+  <si>
+    <t>EP3720</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032028390499</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538470PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:28:39.997</t>
+  </si>
+  <si>
+    <t>6903.06</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;09/08/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032028580500</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538471PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:28:58.847</t>
+  </si>
+  <si>
+    <t>02633187000196&amp;08/09/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202608031947000231</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85530900PO</t>
+  </si>
+  <si>
+    <t>2026-08-03 19:47:00.287</t>
+  </si>
+  <si>
+    <t>22688889000346&amp;01/09/2026&amp;3010</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032001410458</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538427PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:01:42.14</t>
+  </si>
+  <si>
+    <t>2500.00</t>
+  </si>
+  <si>
+    <t>21525889000109&amp;NA</t>
+  </si>
+  <si>
+    <t>17.02</t>
+  </si>
+  <si>
+    <t>B71668</t>
+  </si>
+  <si>
+    <t>ASG TREINAMENTO E SERVICOS</t>
+  </si>
+  <si>
+    <t>EP14610</t>
+  </si>
+  <si>
+    <t>Roberto Ferreira</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032004380469</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538438PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:04:38.51</t>
+  </si>
+  <si>
+    <t>2336.10</t>
+  </si>
+  <si>
+    <t>45786788000141&amp;NA</t>
+  </si>
+  <si>
+    <t>B73100</t>
+  </si>
+  <si>
+    <t>QUALI TECH SER CON AUTO LTDA</t>
+  </si>
+  <si>
+    <t>EP14467</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032019590470</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538440PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:19:59.717</t>
+  </si>
+  <si>
+    <t>4400.52</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032020180471</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538441PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:20:18.547</t>
+  </si>
+  <si>
+    <t>2246.74</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032021070472</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538443PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:21:07.57</t>
+  </si>
+  <si>
+    <t>1051.79</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032021260473</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538444PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:21:26.907</t>
+  </si>
+  <si>
+    <t>12943.88</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032021450474</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538445PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:21:45.74</t>
+  </si>
+  <si>
+    <t>1795.17</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032023250480</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538451PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:23:26.073</t>
+  </si>
+  <si>
+    <t>128365.44</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032027390495</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538466PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:27:39.913</t>
+  </si>
+  <si>
+    <t>37884.63</t>
+  </si>
+  <si>
+    <t>02633186000141&amp;08/09/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032027580496</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538467PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:27:58.71</t>
+  </si>
+  <si>
+    <t>24093.12</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609041348380608</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538742PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 13:48:38.467</t>
+  </si>
+  <si>
+    <t>78842.31</t>
+  </si>
+  <si>
+    <t>05490840000101&amp;09/10/2026</t>
+  </si>
+  <si>
+    <t>17.19</t>
+  </si>
+  <si>
+    <t>B73166</t>
+  </si>
+  <si>
+    <t>KPMG ASSESSORES LTDA</t>
+  </si>
+  <si>
+    <t>EP15204</t>
+  </si>
+  <si>
+    <t>Vera Cavalcante</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609041349340611</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538745PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 13:49:35.08</t>
+  </si>
+  <si>
+    <t>3478.37</t>
+  </si>
+  <si>
+    <t>EP14632</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609041617450621</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538814PO</t>
+  </si>
+  <si>
+    <t>2026-09-04 16:17:46.117</t>
+  </si>
+  <si>
+    <t>4922.64</t>
+  </si>
+  <si>
+    <t>272246&amp;01</t>
+  </si>
+  <si>
+    <t>31861323000527&amp;02/09/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032029170501</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538472PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:29:17.73</t>
+  </si>
+  <si>
+    <t>25792.33</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032029360502</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538473PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:29:36.547</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032029400503</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538474PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:29:40.17</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032029580504</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538475PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:29:58.993</t>
+  </si>
+  <si>
+    <t>462.66</t>
+  </si>
+  <si>
+    <t>18756022000141&amp;10/10/2026</t>
+  </si>
+  <si>
+    <t>B71295</t>
+  </si>
+  <si>
+    <t>COMPASS LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>EP168357</t>
+  </si>
+  <si>
+    <t>Andre Morais</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032030170505</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538476PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:30:17.863</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032030370506</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538477PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:30:37.717</t>
+  </si>
+  <si>
+    <t>430.00</t>
+  </si>
+  <si>
+    <t>18756022000141&amp;01/10/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032030560507</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538478PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:30:56.637</t>
+  </si>
+  <si>
+    <t>18756022000141&amp;05/10/2026</t>
+  </si>
+  <si>
+    <t>SKFAUTOAPE202609032032340513</t>
+  </si>
+  <si>
+    <t>EmailRefSKF9645L85538484PO</t>
+  </si>
+  <si>
+    <t>2026-09-03 20:32:34.64</t>
+  </si>
+  <si>
+    <t>13040.00</t>
+  </si>
+  <si>
+    <t>07846117000130&amp;23/09/2026</t>
+  </si>
+  <si>
+    <t>B68565</t>
+  </si>
+  <si>
+    <t>MULTMOTORES COM.E REP.DE MOTOR</t>
+  </si>
+  <si>
+    <t>EP1642028</t>
+  </si>
+  <si>
+    <t>CNPJ divergente</t>
   </si>
 </sst>
 </file>
@@ -1220,10 +1487,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1605,16 +1868,16 @@
         <v>11</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>13</v>
@@ -1629,2761 +1892,3364 @@
         <v>16</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="B2" t="s">
-        <v>167</v>
+        <v>210</v>
       </c>
       <c r="C2" t="s">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="G2" t="s">
         <v>18</v>
       </c>
       <c r="H2">
-        <v>184</v>
+        <v>206309</v>
       </c>
       <c r="I2" s="1">
-        <v>46254</v>
+        <v>46253</v>
       </c>
       <c r="J2">
-        <v>45544.78</v>
+        <v>8407.2199999999993</v>
       </c>
       <c r="K2" t="s">
-        <v>170</v>
+        <v>213</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
       </c>
+      <c r="M2" t="s">
+        <v>192</v>
+      </c>
       <c r="O2" t="s">
-        <v>171</v>
+        <v>214</v>
       </c>
       <c r="P2" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="Q2" t="s">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="R2" t="s">
         <v>20</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T2" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="U2" t="s">
-        <v>63</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>94</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>177</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="G3" t="s">
         <v>18</v>
       </c>
       <c r="H3">
-        <v>89</v>
+        <v>18</v>
       </c>
       <c r="I3" s="1">
-        <v>46254</v>
+        <v>46072</v>
       </c>
       <c r="J3">
-        <v>6130</v>
+        <v>36939.5</v>
       </c>
       <c r="K3" t="s">
-        <v>179</v>
+        <v>98</v>
       </c>
       <c r="L3" t="s">
         <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>60</v>
+        <v>99</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
       </c>
       <c r="O3" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="P3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q3" t="s">
-        <v>180</v>
+        <v>102</v>
       </c>
       <c r="R3" t="s">
         <v>20</v>
       </c>
       <c r="S3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T3" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="U3" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="G4" t="s">
         <v>18</v>
       </c>
       <c r="H4">
-        <v>18</v>
+        <v>95900</v>
       </c>
       <c r="I4" s="1">
-        <v>46072</v>
+        <v>46245</v>
       </c>
       <c r="J4">
-        <v>36939.5</v>
+        <v>4950</v>
       </c>
       <c r="K4" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="L4" t="s">
         <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>114</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="O4" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="P4" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="Q4" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="R4" t="s">
         <v>20</v>
       </c>
       <c r="S4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T4" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="U4" t="s">
-        <v>252</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>122</v>
+        <v>220</v>
       </c>
       <c r="G5" t="s">
         <v>18</v>
       </c>
       <c r="H5">
-        <v>13371</v>
+        <v>330285</v>
       </c>
       <c r="I5" s="1">
-        <v>46245</v>
+        <v>46266</v>
       </c>
       <c r="J5">
-        <v>17900</v>
+        <v>4942.72</v>
       </c>
       <c r="K5" t="s">
-        <v>123</v>
+        <v>221</v>
       </c>
       <c r="L5" t="s">
         <v>19</v>
       </c>
-      <c r="M5" t="s">
-        <v>114</v>
-      </c>
       <c r="O5" t="s">
-        <v>124</v>
+        <v>222</v>
       </c>
       <c r="P5" t="s">
-        <v>125</v>
+        <v>223</v>
       </c>
       <c r="Q5" t="s">
-        <v>126</v>
+        <v>35</v>
       </c>
       <c r="R5" t="s">
         <v>20</v>
       </c>
       <c r="S5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T5" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="U5" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>224</v>
       </c>
       <c r="B6" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="D6" t="s">
         <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>227</v>
       </c>
       <c r="G6" t="s">
         <v>18</v>
       </c>
       <c r="H6">
-        <v>95900</v>
+        <v>11210</v>
       </c>
       <c r="I6" s="1">
-        <v>46245</v>
+        <v>46268</v>
       </c>
       <c r="J6">
-        <v>4950</v>
+        <v>3346</v>
       </c>
       <c r="K6" t="s">
-        <v>186</v>
+        <v>228</v>
       </c>
       <c r="L6" t="s">
         <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>187</v>
+        <v>45</v>
       </c>
       <c r="O6" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="P6" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="Q6" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="R6" t="s">
         <v>20</v>
       </c>
       <c r="S6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T6" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="U6" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>233</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>235</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
         <v>18</v>
       </c>
       <c r="H7">
-        <v>32739</v>
+        <v>30651</v>
       </c>
       <c r="I7" s="1">
-        <v>46150</v>
+        <v>46266</v>
       </c>
       <c r="J7">
-        <v>4961.32</v>
+        <v>17036.599999999999</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L7" t="s">
         <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P7" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="Q7" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" t="s">
+        <v>20</v>
+      </c>
+      <c r="S7" t="s">
+        <v>34</v>
+      </c>
+      <c r="T7" t="s">
+        <v>87</v>
+      </c>
+      <c r="U7" t="s">
         <v>193</v>
-      </c>
-      <c r="R7" t="s">
-        <v>20</v>
-      </c>
-      <c r="S7" t="s">
-        <v>44</v>
-      </c>
-      <c r="T7" t="s">
-        <v>194</v>
-      </c>
-      <c r="U7" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
+        <v>238</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s">
+        <v>239</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8">
+        <v>5565049</v>
+      </c>
+      <c r="I8" s="1">
+        <v>46262</v>
+      </c>
+      <c r="J8">
+        <v>1162.95</v>
+      </c>
+      <c r="K8" t="s">
+        <v>240</v>
+      </c>
+      <c r="L8" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" t="s">
+        <v>241</v>
+      </c>
+      <c r="P8" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>35</v>
+      </c>
+      <c r="R8" t="s">
+        <v>20</v>
+      </c>
+      <c r="S8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8">
-        <v>22890</v>
-      </c>
-      <c r="I8" s="1">
-        <v>46204</v>
-      </c>
-      <c r="J8">
-        <v>17036.599999999999</v>
-      </c>
-      <c r="K8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" t="s">
-        <v>56</v>
-      </c>
-      <c r="O8" t="s">
-        <v>37</v>
-      </c>
-      <c r="P8" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>38</v>
-      </c>
-      <c r="R8" t="s">
-        <v>20</v>
-      </c>
-      <c r="S8" t="s">
-        <v>43</v>
-      </c>
       <c r="T8" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="U8" t="s">
-        <v>252</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B9" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C9" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D9" t="s">
         <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="G9" t="s">
         <v>18</v>
       </c>
       <c r="H9">
-        <v>75</v>
+        <v>2152</v>
       </c>
       <c r="I9" s="1">
-        <v>46220</v>
+        <v>46267</v>
       </c>
       <c r="J9">
-        <v>12424</v>
+        <v>37500</v>
       </c>
       <c r="K9" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="L9" t="s">
         <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="O9" t="s">
-        <v>61</v>
+        <v>248</v>
       </c>
       <c r="P9" t="s">
-        <v>104</v>
+        <v>249</v>
       </c>
       <c r="Q9" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="R9" t="s">
         <v>20</v>
       </c>
       <c r="S9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T9" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="U9" t="s">
-        <v>259</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>252</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>199</v>
+        <v>254</v>
       </c>
       <c r="G10" t="s">
         <v>18</v>
       </c>
       <c r="H10">
-        <v>21</v>
+        <v>373</v>
       </c>
       <c r="I10" s="1">
-        <v>46238</v>
+        <v>46268</v>
       </c>
       <c r="J10">
-        <v>100382</v>
+        <v>6280</v>
       </c>
       <c r="K10" t="s">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="L10" t="s">
         <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>201</v>
+        <v>45</v>
       </c>
       <c r="O10" t="s">
-        <v>202</v>
+        <v>256</v>
       </c>
       <c r="P10" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="Q10" t="s">
-        <v>204</v>
+        <v>258</v>
       </c>
       <c r="R10" t="s">
         <v>20</v>
       </c>
       <c r="S10" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T10" t="s">
-        <v>65</v>
+        <v>259</v>
       </c>
       <c r="U10" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>89</v>
+        <v>260</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>261</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>262</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>263</v>
       </c>
       <c r="G11" t="s">
         <v>18</v>
       </c>
       <c r="H11">
-        <v>159</v>
+        <v>381781</v>
       </c>
       <c r="I11" s="1">
-        <v>46238</v>
+        <v>46266</v>
       </c>
       <c r="J11">
-        <v>19309.14</v>
+        <v>827.4</v>
       </c>
       <c r="K11" t="s">
-        <v>93</v>
+        <v>264</v>
       </c>
       <c r="L11" t="s">
         <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>94</v>
+        <v>202</v>
       </c>
       <c r="O11" t="s">
-        <v>95</v>
+        <v>265</v>
       </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>266</v>
       </c>
       <c r="Q11" t="s">
-        <v>96</v>
+        <v>267</v>
       </c>
       <c r="R11" t="s">
         <v>20</v>
       </c>
       <c r="S11" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T11" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="U11" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>269</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>271</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>272</v>
       </c>
       <c r="G12" t="s">
         <v>18</v>
       </c>
       <c r="H12">
-        <v>29090</v>
+        <v>381770</v>
       </c>
       <c r="I12" s="1">
-        <v>46174</v>
+        <v>46266</v>
       </c>
       <c r="J12">
-        <v>588.6</v>
+        <v>44428.52</v>
       </c>
       <c r="K12" t="s">
-        <v>131</v>
+        <v>264</v>
       </c>
       <c r="L12" t="s">
         <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>58</v>
+        <v>202</v>
       </c>
       <c r="O12" t="s">
-        <v>132</v>
+        <v>265</v>
       </c>
       <c r="P12" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="Q12" t="s">
-        <v>134</v>
+        <v>273</v>
       </c>
       <c r="R12" t="s">
         <v>20</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T12" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="U12" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>274</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>275</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>276</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>277</v>
       </c>
       <c r="G13" t="s">
         <v>18</v>
       </c>
       <c r="H13">
-        <v>36993</v>
+        <v>381768</v>
       </c>
       <c r="I13" s="1">
-        <v>46204</v>
+        <v>46266</v>
       </c>
       <c r="J13">
-        <v>1300</v>
+        <v>45639.88</v>
       </c>
       <c r="K13" t="s">
-        <v>50</v>
+        <v>264</v>
       </c>
       <c r="L13" t="s">
         <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>57</v>
+        <v>202</v>
       </c>
       <c r="O13" t="s">
-        <v>51</v>
+        <v>265</v>
       </c>
       <c r="P13" t="s">
-        <v>103</v>
+        <v>266</v>
       </c>
       <c r="Q13" t="s">
-        <v>52</v>
+        <v>273</v>
       </c>
       <c r="R13" t="s">
         <v>20</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T13" t="s">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="U13" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>278</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>279</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>280</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
+        <v>281</v>
       </c>
       <c r="G14" t="s">
         <v>18</v>
       </c>
       <c r="H14">
-        <v>452</v>
+        <v>10004</v>
       </c>
       <c r="I14" s="1">
-        <v>46027</v>
+        <v>46259</v>
       </c>
       <c r="J14">
-        <v>138055</v>
+        <v>600</v>
       </c>
       <c r="K14" t="s">
-        <v>71</v>
+        <v>282</v>
       </c>
       <c r="L14" t="s">
         <v>19</v>
       </c>
       <c r="M14" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="O14" t="s">
-        <v>72</v>
+        <v>283</v>
       </c>
       <c r="P14" t="s">
-        <v>106</v>
+        <v>284</v>
       </c>
       <c r="Q14" t="s">
-        <v>45</v>
+        <v>285</v>
       </c>
       <c r="R14" t="s">
         <v>20</v>
       </c>
       <c r="S14" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T14" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="U14" t="s">
-        <v>252</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>286</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>287</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>288</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>289</v>
       </c>
       <c r="G15" t="s">
         <v>18</v>
       </c>
       <c r="H15">
-        <v>1267</v>
+        <v>1475</v>
       </c>
       <c r="I15" s="1">
-        <v>45957</v>
+        <v>46224</v>
       </c>
       <c r="J15">
-        <v>13243.82</v>
+        <v>15233.36</v>
       </c>
       <c r="K15" t="s">
-        <v>31</v>
+        <v>290</v>
       </c>
       <c r="L15" t="s">
         <v>19</v>
       </c>
-      <c r="O15">
-        <v>22688889000384</v>
+      <c r="M15" t="s">
+        <v>47</v>
+      </c>
+      <c r="O15" t="s">
+        <v>291</v>
       </c>
       <c r="P15" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="Q15" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="R15" t="s">
         <v>20</v>
       </c>
       <c r="S15" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T15" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="U15" t="s">
-        <v>192</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="B16" t="s">
-        <v>262</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
       </c>
       <c r="E16" t="s">
-        <v>264</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
         <v>18</v>
       </c>
       <c r="H16">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="I16" s="1">
-        <v>46248</v>
+        <v>46238</v>
       </c>
       <c r="J16">
-        <v>4680</v>
+        <v>19309.14</v>
       </c>
       <c r="K16" t="s">
-        <v>265</v>
+        <v>80</v>
       </c>
       <c r="L16" t="s">
         <v>19</v>
       </c>
       <c r="M16" t="s">
-        <v>242</v>
+        <v>81</v>
       </c>
       <c r="O16" t="s">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="P16" t="s">
-        <v>267</v>
+        <v>90</v>
       </c>
       <c r="Q16" t="s">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="R16" t="s">
         <v>20</v>
       </c>
       <c r="S16" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T16" t="s">
-        <v>194</v>
+        <v>84</v>
       </c>
       <c r="U16" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>140</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>141</v>
+        <v>39</v>
       </c>
       <c r="G17" t="s">
         <v>18</v>
       </c>
       <c r="H17">
-        <v>35007</v>
+        <v>36993</v>
       </c>
       <c r="I17" s="1">
-        <v>46220</v>
+        <v>46204</v>
       </c>
       <c r="J17">
-        <v>57773.02</v>
+        <v>1300</v>
       </c>
       <c r="K17" t="s">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="L17" t="s">
         <v>19</v>
       </c>
       <c r="M17" t="s">
-        <v>143</v>
+        <v>47</v>
       </c>
       <c r="O17" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
       <c r="P17" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="Q17" t="s">
-        <v>146</v>
+        <v>42</v>
       </c>
       <c r="R17" t="s">
         <v>20</v>
       </c>
       <c r="S17" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="T17" t="s">
-        <v>59</v>
+        <v>294</v>
       </c>
       <c r="U17" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>161</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
         <v>18</v>
       </c>
       <c r="H18">
-        <v>13428</v>
+        <v>452</v>
       </c>
       <c r="I18" s="1">
-        <v>46246</v>
+        <v>46027</v>
       </c>
       <c r="J18">
-        <v>3500</v>
+        <v>138055</v>
       </c>
       <c r="K18" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="L18" t="s">
         <v>19</v>
       </c>
       <c r="M18" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="O18" t="s">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="P18" t="s">
-        <v>164</v>
+        <v>91</v>
       </c>
       <c r="Q18" t="s">
-        <v>165</v>
+        <v>35</v>
       </c>
       <c r="R18" t="s">
         <v>20</v>
       </c>
       <c r="S18" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T18" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="U18" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>217</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
       </c>
       <c r="E19" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
         <v>18</v>
       </c>
       <c r="H19">
-        <v>1138</v>
+        <v>1267</v>
       </c>
       <c r="I19" s="1">
-        <v>46253</v>
+        <v>45957</v>
       </c>
       <c r="J19">
-        <v>2431.64</v>
+        <v>13243.82</v>
       </c>
       <c r="K19" t="s">
-        <v>219</v>
+        <v>25</v>
       </c>
       <c r="L19" t="s">
         <v>19</v>
       </c>
-      <c r="M19" t="s">
-        <v>55</v>
-      </c>
       <c r="O19" t="s">
-        <v>136</v>
+        <v>295</v>
       </c>
       <c r="P19" t="s">
-        <v>137</v>
+        <v>296</v>
       </c>
       <c r="Q19" t="s">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="R19" t="s">
         <v>20</v>
       </c>
       <c r="S19" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T19" t="s">
-        <v>221</v>
+        <v>52</v>
       </c>
       <c r="U19" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>104</v>
       </c>
       <c r="B20" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>208</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>209</v>
+        <v>107</v>
       </c>
       <c r="G20" t="s">
         <v>18</v>
       </c>
       <c r="H20">
-        <v>76555</v>
+        <v>29090</v>
       </c>
       <c r="I20" s="1">
-        <v>46253</v>
+        <v>46174</v>
       </c>
       <c r="J20">
-        <v>429.79</v>
+        <v>588.6</v>
       </c>
       <c r="K20" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="L20" t="s">
         <v>19</v>
       </c>
+      <c r="M20" t="s">
+        <v>48</v>
+      </c>
       <c r="O20" t="s">
-        <v>211</v>
+        <v>109</v>
       </c>
       <c r="P20" t="s">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="Q20" t="s">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="R20" t="s">
         <v>20</v>
       </c>
       <c r="S20" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="T20" t="s">
-        <v>214</v>
+        <v>103</v>
       </c>
       <c r="U20" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>297</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>298</v>
       </c>
       <c r="C21" t="s">
-        <v>75</v>
+        <v>299</v>
       </c>
       <c r="D21" t="s">
         <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>300</v>
       </c>
       <c r="G21" t="s">
         <v>18</v>
       </c>
       <c r="H21">
-        <v>73150</v>
+        <v>7566</v>
       </c>
       <c r="I21" s="1">
-        <v>46211</v>
+        <v>46269</v>
       </c>
       <c r="J21">
-        <v>31736.080000000002</v>
+        <v>9441.99</v>
       </c>
       <c r="K21" t="s">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="L21" t="s">
         <v>19</v>
       </c>
       <c r="M21" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="O21" t="s">
-        <v>79</v>
+        <v>302</v>
       </c>
       <c r="P21" t="s">
-        <v>107</v>
+        <v>303</v>
       </c>
       <c r="Q21" t="s">
-        <v>80</v>
+        <v>304</v>
       </c>
       <c r="R21" t="s">
         <v>20</v>
       </c>
       <c r="S21" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T21" t="s">
-        <v>81</v>
+        <v>305</v>
       </c>
       <c r="U21" t="s">
-        <v>252</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B22" t="s">
-        <v>223</v>
+        <v>307</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>308</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>225</v>
+        <v>309</v>
       </c>
       <c r="G22" t="s">
         <v>18</v>
       </c>
       <c r="H22">
-        <v>1730217184</v>
+        <v>59</v>
       </c>
       <c r="I22" s="1">
-        <v>46211</v>
+        <v>46269</v>
       </c>
       <c r="J22">
-        <v>31736.080000000002</v>
+        <v>15700</v>
       </c>
       <c r="K22" t="s">
-        <v>226</v>
+        <v>310</v>
       </c>
       <c r="L22" t="s">
         <v>19</v>
       </c>
+      <c r="M22" t="s">
+        <v>311</v>
+      </c>
       <c r="O22" t="s">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="P22" t="s">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="Q22" t="s">
-        <v>228</v>
+        <v>314</v>
       </c>
       <c r="R22" t="s">
         <v>20</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="T22" t="s">
-        <v>81</v>
+        <v>315</v>
       </c>
       <c r="U22" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>270</v>
+        <v>316</v>
       </c>
       <c r="B23" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="C23" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
       </c>
       <c r="E23" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="G23" t="s">
         <v>18</v>
       </c>
       <c r="H23">
-        <v>31329</v>
+        <v>16</v>
       </c>
       <c r="I23" s="1">
-        <v>46253</v>
+        <v>46266</v>
       </c>
       <c r="J23">
-        <v>4638.72</v>
+        <v>660</v>
       </c>
       <c r="K23" t="s">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="L23" t="s">
         <v>19</v>
       </c>
+      <c r="M23" t="s">
+        <v>45</v>
+      </c>
       <c r="O23" t="s">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="P23" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="Q23" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="R23" t="s">
         <v>20</v>
       </c>
       <c r="S23" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T23" t="s">
-        <v>278</v>
+        <v>324</v>
       </c>
       <c r="U23" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>229</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
-        <v>230</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>231</v>
+        <v>117</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>232</v>
+        <v>118</v>
       </c>
       <c r="G24" t="s">
         <v>18</v>
       </c>
       <c r="H24">
-        <v>2409</v>
+        <v>35007</v>
       </c>
       <c r="I24" s="1">
-        <v>46253</v>
+        <v>46220</v>
       </c>
       <c r="J24">
-        <v>51240</v>
+        <v>57773.02</v>
       </c>
       <c r="K24" t="s">
-        <v>233</v>
+        <v>119</v>
       </c>
       <c r="L24" t="s">
         <v>19</v>
       </c>
       <c r="M24" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="O24" t="s">
-        <v>234</v>
+        <v>121</v>
       </c>
       <c r="P24" t="s">
-        <v>235</v>
+        <v>122</v>
       </c>
       <c r="Q24" t="s">
-        <v>236</v>
+        <v>123</v>
       </c>
       <c r="R24" t="s">
         <v>20</v>
       </c>
       <c r="S24" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T24" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="U24" t="s">
-        <v>157</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>237</v>
+        <v>325</v>
       </c>
       <c r="B25" t="s">
-        <v>238</v>
+        <v>326</v>
       </c>
       <c r="C25" t="s">
-        <v>239</v>
+        <v>327</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>240</v>
+        <v>328</v>
       </c>
       <c r="G25" t="s">
         <v>18</v>
       </c>
       <c r="H25">
-        <v>2408</v>
+        <v>15552</v>
       </c>
       <c r="I25" s="1">
-        <v>46253</v>
+        <v>46247</v>
       </c>
       <c r="J25">
-        <v>54600</v>
+        <v>6617.3</v>
       </c>
       <c r="K25" t="s">
-        <v>241</v>
+        <v>329</v>
       </c>
       <c r="L25" t="s">
         <v>19</v>
       </c>
       <c r="M25" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="O25" t="s">
-        <v>234</v>
+        <v>330</v>
       </c>
       <c r="P25" t="s">
-        <v>235</v>
+        <v>331</v>
       </c>
       <c r="Q25" t="s">
-        <v>236</v>
+        <v>332</v>
       </c>
       <c r="R25" t="s">
         <v>20</v>
       </c>
       <c r="S25" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T25" t="s">
-        <v>100</v>
+        <v>333</v>
       </c>
       <c r="U25" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>243</v>
+        <v>135</v>
       </c>
       <c r="B26" t="s">
-        <v>244</v>
+        <v>136</v>
       </c>
       <c r="C26" t="s">
-        <v>245</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="G26" t="s">
         <v>18</v>
       </c>
       <c r="H26">
-        <v>245</v>
+        <v>13428</v>
       </c>
       <c r="I26" s="1">
-        <v>46253</v>
+        <v>46246</v>
       </c>
       <c r="J26">
-        <v>23760</v>
+        <v>3500</v>
       </c>
       <c r="K26" t="s">
-        <v>247</v>
+        <v>139</v>
       </c>
       <c r="L26" t="s">
         <v>19</v>
       </c>
       <c r="M26" t="s">
-        <v>248</v>
+        <v>85</v>
       </c>
       <c r="O26" t="s">
-        <v>249</v>
+        <v>140</v>
       </c>
       <c r="P26" t="s">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="Q26" t="s">
-        <v>251</v>
+        <v>142</v>
       </c>
       <c r="R26" t="s">
         <v>20</v>
       </c>
       <c r="S26" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T26" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="U26" t="s">
-        <v>195</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>279</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s">
-        <v>280</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
-        <v>281</v>
+        <v>159</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>282</v>
+        <v>160</v>
       </c>
       <c r="G27" t="s">
         <v>18</v>
       </c>
       <c r="H27">
-        <v>15372</v>
+        <v>76555</v>
       </c>
       <c r="I27" s="1">
-        <v>46241</v>
+        <v>46253</v>
       </c>
       <c r="J27">
-        <v>105122.59</v>
+        <v>429.79</v>
       </c>
       <c r="K27" t="s">
-        <v>283</v>
+        <v>161</v>
       </c>
       <c r="L27" t="s">
         <v>19</v>
       </c>
-      <c r="M27" t="s">
-        <v>284</v>
-      </c>
       <c r="O27" t="s">
-        <v>285</v>
+        <v>162</v>
       </c>
       <c r="P27" t="s">
-        <v>286</v>
+        <v>163</v>
       </c>
       <c r="Q27" t="s">
-        <v>287</v>
+        <v>164</v>
       </c>
       <c r="R27" t="s">
         <v>20</v>
       </c>
       <c r="S27" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T27" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="U27" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>288</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>289</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>290</v>
+        <v>62</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>291</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
         <v>18</v>
       </c>
       <c r="H28">
-        <v>15262</v>
+        <v>73150</v>
       </c>
       <c r="I28" s="1">
-        <v>46153</v>
+        <v>46211</v>
       </c>
       <c r="J28">
-        <v>9372.24</v>
+        <v>31736.080000000002</v>
       </c>
       <c r="K28" t="s">
-        <v>292</v>
+        <v>64</v>
       </c>
       <c r="L28" t="s">
         <v>19</v>
       </c>
       <c r="M28" t="s">
-        <v>284</v>
+        <v>65</v>
       </c>
       <c r="O28" t="s">
-        <v>285</v>
+        <v>66</v>
       </c>
       <c r="P28" t="s">
-        <v>286</v>
+        <v>92</v>
       </c>
       <c r="Q28" t="s">
-        <v>287</v>
+        <v>67</v>
       </c>
       <c r="R28" t="s">
         <v>20</v>
       </c>
       <c r="S28" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T28" t="s">
-        <v>221</v>
+        <v>68</v>
       </c>
       <c r="U28" t="s">
-        <v>293</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>294</v>
+        <v>172</v>
       </c>
       <c r="B29" t="s">
-        <v>295</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>296</v>
+        <v>174</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>297</v>
+        <v>175</v>
       </c>
       <c r="G29" t="s">
         <v>18</v>
       </c>
       <c r="H29">
-        <v>15371</v>
+        <v>1730217184</v>
       </c>
       <c r="I29" s="1">
-        <v>46241</v>
+        <v>46211</v>
       </c>
       <c r="J29">
-        <v>1073.56</v>
+        <v>31736.080000000002</v>
       </c>
       <c r="K29" t="s">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="L29" t="s">
         <v>19</v>
       </c>
-      <c r="M29" t="s">
-        <v>284</v>
-      </c>
       <c r="O29" t="s">
-        <v>285</v>
+        <v>177</v>
       </c>
       <c r="P29" t="s">
-        <v>286</v>
+        <v>194</v>
       </c>
       <c r="Q29" t="s">
-        <v>287</v>
+        <v>178</v>
       </c>
       <c r="R29" t="s">
         <v>20</v>
       </c>
       <c r="S29" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="T29" t="s">
-        <v>221</v>
+        <v>68</v>
       </c>
       <c r="U29" t="s">
-        <v>215</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>298</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>299</v>
+        <v>168</v>
       </c>
       <c r="C30" t="s">
-        <v>300</v>
+        <v>169</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>297</v>
+        <v>112</v>
       </c>
       <c r="G30" t="s">
         <v>18</v>
       </c>
       <c r="H30">
-        <v>15257</v>
+        <v>1138</v>
       </c>
       <c r="I30" s="1">
-        <v>46150</v>
+        <v>46253</v>
       </c>
       <c r="J30">
-        <v>1073.56</v>
+        <v>2431.64</v>
       </c>
       <c r="K30" t="s">
-        <v>301</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s">
         <v>19</v>
       </c>
       <c r="M30" t="s">
-        <v>284</v>
+        <v>45</v>
       </c>
       <c r="O30" t="s">
-        <v>285</v>
+        <v>113</v>
       </c>
       <c r="P30" t="s">
-        <v>286</v>
+        <v>114</v>
       </c>
       <c r="Q30" t="s">
-        <v>287</v>
+        <v>334</v>
       </c>
       <c r="R30" t="s">
         <v>20</v>
       </c>
       <c r="S30" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T30" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U30" t="s">
-        <v>215</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="B31" t="s">
-        <v>303</v>
+        <v>336</v>
       </c>
       <c r="C31" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
       </c>
       <c r="E31" t="s">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="G31" t="s">
         <v>18</v>
       </c>
       <c r="H31">
-        <v>27421</v>
+        <v>15305</v>
       </c>
       <c r="I31" s="1">
-        <v>46241</v>
+        <v>46183</v>
       </c>
       <c r="J31">
-        <v>603.65</v>
+        <v>8591.2199999999993</v>
       </c>
       <c r="K31" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="L31" t="s">
         <v>19</v>
       </c>
       <c r="M31" t="s">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="O31" t="s">
-        <v>308</v>
+        <v>197</v>
       </c>
       <c r="P31" t="s">
-        <v>309</v>
+        <v>198</v>
       </c>
       <c r="Q31" t="s">
-        <v>310</v>
+        <v>199</v>
       </c>
       <c r="R31" t="s">
         <v>20</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T31" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U31" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s">
-        <v>312</v>
+        <v>341</v>
       </c>
       <c r="C32" t="s">
-        <v>313</v>
+        <v>342</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
       </c>
       <c r="E32" t="s">
-        <v>314</v>
+        <v>195</v>
       </c>
       <c r="G32" t="s">
         <v>18</v>
       </c>
       <c r="H32">
-        <v>27475</v>
+        <v>15302</v>
       </c>
       <c r="I32" s="1">
-        <v>46251</v>
+        <v>46183</v>
       </c>
       <c r="J32">
-        <v>13680</v>
+        <v>105122.59</v>
       </c>
       <c r="K32" t="s">
-        <v>315</v>
+        <v>343</v>
       </c>
       <c r="L32" t="s">
         <v>19</v>
       </c>
       <c r="M32" t="s">
-        <v>307</v>
+        <v>196</v>
       </c>
       <c r="O32" t="s">
-        <v>308</v>
+        <v>197</v>
       </c>
       <c r="P32" t="s">
-        <v>309</v>
+        <v>198</v>
       </c>
       <c r="Q32" t="s">
-        <v>310</v>
+        <v>199</v>
       </c>
       <c r="R32" t="s">
         <v>20</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T32" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U32" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>316</v>
+        <v>179</v>
       </c>
       <c r="B33" t="s">
-        <v>317</v>
+        <v>180</v>
       </c>
       <c r="C33" t="s">
-        <v>318</v>
+        <v>181</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
       </c>
       <c r="E33" t="s">
-        <v>319</v>
+        <v>182</v>
       </c>
       <c r="G33" t="s">
         <v>18</v>
       </c>
       <c r="H33">
-        <v>27047</v>
+        <v>2409</v>
       </c>
       <c r="I33" s="1">
-        <v>46153</v>
+        <v>46253</v>
       </c>
       <c r="J33">
-        <v>56935.15</v>
+        <v>51240</v>
       </c>
       <c r="K33" t="s">
-        <v>320</v>
+        <v>183</v>
       </c>
       <c r="L33" t="s">
         <v>19</v>
       </c>
       <c r="M33" t="s">
-        <v>284</v>
+        <v>48</v>
       </c>
       <c r="O33" t="s">
-        <v>308</v>
+        <v>184</v>
       </c>
       <c r="P33" t="s">
-        <v>309</v>
+        <v>185</v>
       </c>
       <c r="Q33" t="s">
-        <v>310</v>
+        <v>186</v>
       </c>
       <c r="R33" t="s">
         <v>20</v>
       </c>
       <c r="S33" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T33" t="s">
-        <v>221</v>
+        <v>87</v>
       </c>
       <c r="U33" t="s">
-        <v>293</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>321</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>322</v>
+        <v>188</v>
       </c>
       <c r="C34" t="s">
-        <v>323</v>
+        <v>189</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
       </c>
       <c r="E34" t="s">
-        <v>324</v>
+        <v>190</v>
       </c>
       <c r="G34" t="s">
         <v>18</v>
       </c>
       <c r="H34">
-        <v>15384</v>
+        <v>2408</v>
       </c>
       <c r="I34" s="1">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="J34">
-        <v>10153.26</v>
+        <v>54600</v>
       </c>
       <c r="K34" t="s">
-        <v>325</v>
+        <v>191</v>
       </c>
       <c r="L34" t="s">
         <v>19</v>
       </c>
       <c r="M34" t="s">
-        <v>284</v>
+        <v>48</v>
       </c>
       <c r="O34" t="s">
-        <v>285</v>
+        <v>184</v>
       </c>
       <c r="P34" t="s">
-        <v>286</v>
+        <v>185</v>
       </c>
       <c r="Q34" t="s">
-        <v>287</v>
+        <v>186</v>
       </c>
       <c r="R34" t="s">
         <v>20</v>
       </c>
       <c r="S34" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T34" t="s">
-        <v>221</v>
+        <v>87</v>
       </c>
       <c r="U34" t="s">
-        <v>215</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C35" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
       </c>
       <c r="E35" t="s">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="G35" t="s">
         <v>18</v>
       </c>
       <c r="H35">
-        <v>15369</v>
+        <v>1476</v>
       </c>
       <c r="I35" s="1">
-        <v>46241</v>
+        <v>46224</v>
       </c>
       <c r="J35">
-        <v>16167.19</v>
+        <v>13243.82</v>
       </c>
       <c r="K35" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="L35" t="s">
         <v>19</v>
       </c>
       <c r="M35" t="s">
-        <v>284</v>
+        <v>47</v>
       </c>
       <c r="O35" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="P35" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="Q35" t="s">
-        <v>330</v>
+        <v>156</v>
       </c>
       <c r="R35" t="s">
         <v>20</v>
       </c>
       <c r="S35" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T35" t="s">
-        <v>221</v>
+        <v>52</v>
       </c>
       <c r="U35" t="s">
-        <v>215</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="C36" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
       </c>
       <c r="E36" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="G36" t="s">
         <v>18</v>
       </c>
       <c r="H36">
-        <v>15263</v>
+        <v>1866</v>
       </c>
       <c r="I36" s="1">
-        <v>46153</v>
+        <v>46267</v>
       </c>
       <c r="J36">
-        <v>13277.34</v>
+        <v>2500</v>
       </c>
       <c r="K36" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="L36" t="s">
         <v>19</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
       <c r="O36" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="P36" t="s">
-        <v>286</v>
+        <v>355</v>
       </c>
       <c r="Q36" t="s">
-        <v>287</v>
+        <v>356</v>
       </c>
       <c r="R36" t="s">
         <v>20</v>
       </c>
       <c r="S36" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T36" t="s">
-        <v>221</v>
+        <v>357</v>
       </c>
       <c r="U36" t="s">
-        <v>293</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C37" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="G37" t="s">
         <v>18</v>
       </c>
       <c r="H37">
-        <v>15385</v>
+        <v>61</v>
       </c>
       <c r="I37" s="1">
-        <v>46251</v>
+        <v>46268</v>
       </c>
       <c r="J37">
-        <v>8591.2199999999993</v>
+        <v>2336.1</v>
       </c>
       <c r="K37" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="L37" t="s">
         <v>19</v>
       </c>
       <c r="M37" t="s">
-        <v>284</v>
+        <v>45</v>
       </c>
       <c r="O37" t="s">
-        <v>285</v>
+        <v>363</v>
       </c>
       <c r="P37" t="s">
-        <v>286</v>
+        <v>364</v>
       </c>
       <c r="Q37" t="s">
-        <v>287</v>
+        <v>365</v>
       </c>
       <c r="R37" t="s">
         <v>20</v>
       </c>
       <c r="S37" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T37" t="s">
-        <v>221</v>
+        <v>87</v>
       </c>
       <c r="U37" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="C38" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="G38" t="s">
         <v>18</v>
       </c>
       <c r="H38">
-        <v>15370</v>
+        <v>381856</v>
       </c>
       <c r="I38" s="1">
-        <v>46241</v>
+        <v>46267</v>
       </c>
       <c r="J38">
-        <v>77833.64</v>
+        <v>5545.7</v>
       </c>
       <c r="K38" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="L38" t="s">
         <v>19</v>
       </c>
       <c r="M38" t="s">
-        <v>284</v>
+        <v>202</v>
       </c>
       <c r="O38" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="P38" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="Q38" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="R38" t="s">
         <v>20</v>
       </c>
       <c r="S38" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T38" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U38" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>345</v>
+        <v>370</v>
       </c>
       <c r="B39" t="s">
-        <v>346</v>
+        <v>371</v>
       </c>
       <c r="C39" t="s">
-        <v>347</v>
+        <v>372</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
       </c>
       <c r="E39" t="s">
-        <v>282</v>
+        <v>373</v>
       </c>
       <c r="G39" t="s">
         <v>18</v>
       </c>
       <c r="H39">
-        <v>15258</v>
+        <v>381846</v>
       </c>
       <c r="I39" s="1">
-        <v>46150</v>
+        <v>46267</v>
       </c>
       <c r="J39">
-        <v>105122.59</v>
+        <v>2831.4</v>
       </c>
       <c r="K39" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="L39" t="s">
         <v>19</v>
       </c>
       <c r="M39" t="s">
-        <v>284</v>
+        <v>202</v>
       </c>
       <c r="O39" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="P39" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="Q39" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="R39" t="s">
         <v>20</v>
       </c>
       <c r="S39" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T39" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U39" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="B40" t="s">
-        <v>349</v>
+        <v>375</v>
       </c>
       <c r="C40" t="s">
-        <v>350</v>
+        <v>376</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="G40" t="s">
         <v>18</v>
       </c>
       <c r="H40">
-        <v>15259</v>
+        <v>381838</v>
       </c>
       <c r="I40" s="1">
-        <v>46150</v>
+        <v>46267</v>
       </c>
       <c r="J40">
-        <v>32324</v>
+        <v>1325.48</v>
       </c>
       <c r="K40" t="s">
-        <v>352</v>
+        <v>264</v>
       </c>
       <c r="L40" t="s">
         <v>19</v>
       </c>
       <c r="M40" t="s">
-        <v>284</v>
+        <v>202</v>
       </c>
       <c r="O40" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="P40" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="Q40" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="R40" t="s">
         <v>20</v>
       </c>
       <c r="S40" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T40" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U40" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="B41" t="s">
-        <v>354</v>
+        <v>379</v>
       </c>
       <c r="C41" t="s">
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="G41" t="s">
         <v>18</v>
       </c>
       <c r="H41">
-        <v>15260</v>
+        <v>381834</v>
       </c>
       <c r="I41" s="1">
-        <v>46150</v>
+        <v>46267</v>
       </c>
       <c r="J41">
-        <v>10153.26</v>
+        <v>16312.37</v>
       </c>
       <c r="K41" t="s">
-        <v>352</v>
+        <v>264</v>
       </c>
       <c r="L41" t="s">
         <v>19</v>
       </c>
       <c r="M41" t="s">
-        <v>284</v>
+        <v>202</v>
       </c>
       <c r="O41" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="P41" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="Q41" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="R41" t="s">
         <v>20</v>
       </c>
       <c r="S41" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T41" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U41" t="s">
-        <v>293</v>
+        <v>268</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="C42" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="G42" t="s">
         <v>18</v>
       </c>
       <c r="H42">
-        <v>15256</v>
+        <v>381829</v>
       </c>
       <c r="I42" s="1">
-        <v>46150</v>
+        <v>46267</v>
       </c>
       <c r="J42">
-        <v>77833.64</v>
+        <v>2262.34</v>
       </c>
       <c r="K42" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="L42" t="s">
         <v>19</v>
       </c>
       <c r="M42" t="s">
-        <v>284</v>
+        <v>202</v>
       </c>
       <c r="O42" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="P42" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="Q42" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="R42" t="s">
         <v>20</v>
       </c>
       <c r="S42" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T42" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U42" t="s">
-        <v>293</v>
+        <v>166</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="C43" t="s">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="G43" t="s">
         <v>18</v>
       </c>
       <c r="H43">
-        <v>27422</v>
+        <v>381765</v>
       </c>
       <c r="I43" s="1">
-        <v>46241</v>
+        <v>46266</v>
       </c>
       <c r="J43">
-        <v>51307.73</v>
+        <v>161771.18</v>
       </c>
       <c r="K43" t="s">
-        <v>306</v>
+        <v>264</v>
       </c>
       <c r="L43" t="s">
         <v>19</v>
       </c>
       <c r="M43" t="s">
-        <v>307</v>
+        <v>202</v>
       </c>
       <c r="O43" t="s">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="P43" t="s">
-        <v>309</v>
+        <v>266</v>
       </c>
       <c r="Q43" t="s">
-        <v>310</v>
+        <v>273</v>
       </c>
       <c r="R43" t="s">
         <v>20</v>
       </c>
       <c r="S43" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T43" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="U43" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="C44" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>305</v>
+        <v>393</v>
       </c>
       <c r="G44" t="s">
         <v>18</v>
       </c>
       <c r="H44">
-        <v>27474</v>
+        <v>27184</v>
       </c>
       <c r="I44" s="1">
-        <v>46251</v>
+        <v>46183</v>
       </c>
       <c r="J44">
-        <v>603.65</v>
+        <v>47743.7</v>
       </c>
       <c r="K44" t="s">
-        <v>315</v>
+        <v>394</v>
       </c>
       <c r="L44" t="s">
         <v>19</v>
       </c>
       <c r="M44" t="s">
-        <v>307</v>
+        <v>202</v>
       </c>
       <c r="O44" t="s">
-        <v>308</v>
+        <v>203</v>
       </c>
       <c r="P44" t="s">
-        <v>309</v>
+        <v>204</v>
       </c>
       <c r="Q44" t="s">
-        <v>310</v>
+        <v>205</v>
       </c>
       <c r="R44" t="s">
         <v>20</v>
       </c>
       <c r="S44" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T44" t="s">
-        <v>221</v>
+        <v>152</v>
       </c>
       <c r="U44" t="s">
-        <v>215</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="C45" t="s">
-        <v>368</v>
+        <v>397</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>369</v>
+        <v>398</v>
       </c>
       <c r="G45" t="s">
         <v>18</v>
       </c>
       <c r="H45">
-        <v>27049</v>
+        <v>27183</v>
       </c>
       <c r="I45" s="1">
-        <v>46153</v>
+        <v>46183</v>
       </c>
       <c r="J45">
-        <v>9865.06</v>
+        <v>30363.1</v>
       </c>
       <c r="K45" t="s">
-        <v>370</v>
+        <v>206</v>
       </c>
       <c r="L45" t="s">
         <v>19</v>
       </c>
       <c r="M45" t="s">
-        <v>307</v>
+        <v>202</v>
       </c>
       <c r="O45" t="s">
-        <v>308</v>
+        <v>203</v>
       </c>
       <c r="P45" t="s">
-        <v>309</v>
+        <v>204</v>
       </c>
       <c r="Q45" t="s">
-        <v>310</v>
+        <v>205</v>
       </c>
       <c r="R45" t="s">
         <v>20</v>
       </c>
       <c r="S45" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="T45" t="s">
-        <v>221</v>
+        <v>152</v>
       </c>
       <c r="U45" t="s">
-        <v>293</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>399</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>400</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>401</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>150</v>
+        <v>402</v>
       </c>
       <c r="G46" t="s">
         <v>18</v>
       </c>
-      <c r="H46" t="s">
-        <v>151</v>
+      <c r="H46">
+        <v>36924</v>
       </c>
       <c r="I46" s="1">
-        <v>46237</v>
+        <v>46268</v>
       </c>
       <c r="J46">
-        <v>14171.56</v>
+        <v>84008.86</v>
       </c>
       <c r="K46" t="s">
-        <v>152</v>
+        <v>403</v>
       </c>
       <c r="L46" t="s">
         <v>19</v>
       </c>
       <c r="M46" t="s">
-        <v>54</v>
+        <v>404</v>
       </c>
       <c r="O46" t="s">
+        <v>405</v>
+      </c>
+      <c r="P46" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>407</v>
+      </c>
+      <c r="R46" t="s">
+        <v>20</v>
+      </c>
+      <c r="S46" t="s">
+        <v>34</v>
+      </c>
+      <c r="T46" t="s">
+        <v>408</v>
+      </c>
+      <c r="U46" t="s">
         <v>153</v>
-      </c>
-      <c r="P46" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>155</v>
-      </c>
-      <c r="R46" t="s">
-        <v>20</v>
-      </c>
-      <c r="S46" t="s">
-        <v>44</v>
-      </c>
-      <c r="T46" t="s">
-        <v>156</v>
-      </c>
-      <c r="U46" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="B47" t="s">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
+        <v>411</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>412</v>
       </c>
       <c r="G47" t="s">
         <v>18</v>
       </c>
       <c r="H47">
+        <v>11214</v>
+      </c>
+      <c r="I47" s="1">
+        <v>46268</v>
+      </c>
+      <c r="J47">
+        <v>3648</v>
+      </c>
+      <c r="K47" t="s">
+        <v>228</v>
+      </c>
+      <c r="L47" t="s">
+        <v>19</v>
+      </c>
+      <c r="M47" t="s">
+        <v>45</v>
+      </c>
+      <c r="O47" t="s">
+        <v>229</v>
+      </c>
+      <c r="P47" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>413</v>
+      </c>
+      <c r="R47" t="s">
+        <v>20</v>
+      </c>
+      <c r="S47" t="s">
+        <v>34</v>
+      </c>
+      <c r="T47" t="s">
+        <v>232</v>
+      </c>
+      <c r="U47" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>414</v>
+      </c>
+      <c r="B48" t="s">
+        <v>415</v>
+      </c>
+      <c r="C48" t="s">
+        <v>416</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" t="s">
+        <v>417</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" t="s">
+        <v>418</v>
+      </c>
+      <c r="I48" s="1">
+        <v>46237</v>
+      </c>
+      <c r="J48">
+        <v>4922.6400000000003</v>
+      </c>
+      <c r="K48" t="s">
+        <v>419</v>
+      </c>
+      <c r="L48" t="s">
+        <v>19</v>
+      </c>
+      <c r="O48" t="s">
+        <v>222</v>
+      </c>
+      <c r="P48" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" t="s">
+        <v>20</v>
+      </c>
+      <c r="S48" t="s">
+        <v>34</v>
+      </c>
+      <c r="T48" t="s">
+        <v>87</v>
+      </c>
+      <c r="U48" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>420</v>
+      </c>
+      <c r="B49" t="s">
+        <v>421</v>
+      </c>
+      <c r="C49" t="s">
+        <v>422</v>
+      </c>
+      <c r="D49" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" t="s">
+        <v>423</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49">
+        <v>15303</v>
+      </c>
+      <c r="I49" s="1">
+        <v>46183</v>
+      </c>
+      <c r="J49">
+        <v>32324</v>
+      </c>
+      <c r="K49" t="s">
+        <v>339</v>
+      </c>
+      <c r="L49" t="s">
+        <v>19</v>
+      </c>
+      <c r="M49" t="s">
+        <v>196</v>
+      </c>
+      <c r="O49" t="s">
+        <v>197</v>
+      </c>
+      <c r="P49" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>199</v>
+      </c>
+      <c r="R49" t="s">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s">
+        <v>34</v>
+      </c>
+      <c r="T49" t="s">
+        <v>171</v>
+      </c>
+      <c r="U49" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>424</v>
+      </c>
+      <c r="B50" t="s">
+        <v>425</v>
+      </c>
+      <c r="C50" t="s">
+        <v>426</v>
+      </c>
+      <c r="D50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E50" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50">
+        <v>15301</v>
+      </c>
+      <c r="I50" s="1">
+        <v>46183</v>
+      </c>
+      <c r="J50">
+        <v>1073.56</v>
+      </c>
+      <c r="K50" t="s">
+        <v>343</v>
+      </c>
+      <c r="L50" t="s">
+        <v>19</v>
+      </c>
+      <c r="M50" t="s">
+        <v>196</v>
+      </c>
+      <c r="O50" t="s">
+        <v>197</v>
+      </c>
+      <c r="P50" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>199</v>
+      </c>
+      <c r="R50" t="s">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s">
+        <v>34</v>
+      </c>
+      <c r="T50" t="s">
+        <v>171</v>
+      </c>
+      <c r="U50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>427</v>
+      </c>
+      <c r="B51" t="s">
+        <v>428</v>
+      </c>
+      <c r="C51" t="s">
+        <v>429</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
+        <v>207</v>
+      </c>
+      <c r="G51" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51">
+        <v>15304</v>
+      </c>
+      <c r="I51" s="1">
+        <v>46183</v>
+      </c>
+      <c r="J51">
+        <v>16167.19</v>
+      </c>
+      <c r="K51" t="s">
+        <v>339</v>
+      </c>
+      <c r="L51" t="s">
+        <v>19</v>
+      </c>
+      <c r="M51" t="s">
+        <v>196</v>
+      </c>
+      <c r="O51" t="s">
+        <v>197</v>
+      </c>
+      <c r="P51" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>199</v>
+      </c>
+      <c r="R51" t="s">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s">
+        <v>34</v>
+      </c>
+      <c r="T51" t="s">
+        <v>171</v>
+      </c>
+      <c r="U51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>430</v>
+      </c>
+      <c r="B52" t="s">
+        <v>431</v>
+      </c>
+      <c r="C52" t="s">
+        <v>432</v>
+      </c>
+      <c r="D52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" t="s">
+        <v>433</v>
+      </c>
+      <c r="G52" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52">
+        <v>45765</v>
+      </c>
+      <c r="I52" s="1">
+        <v>46266</v>
+      </c>
+      <c r="J52">
+        <v>462.66</v>
+      </c>
+      <c r="K52" t="s">
+        <v>434</v>
+      </c>
+      <c r="L52" t="s">
+        <v>19</v>
+      </c>
+      <c r="O52" t="s">
+        <v>435</v>
+      </c>
+      <c r="P52" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>437</v>
+      </c>
+      <c r="R52" t="s">
+        <v>20</v>
+      </c>
+      <c r="S52" t="s">
+        <v>34</v>
+      </c>
+      <c r="T52" t="s">
+        <v>438</v>
+      </c>
+      <c r="U52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>439</v>
+      </c>
+      <c r="B53" t="s">
+        <v>440</v>
+      </c>
+      <c r="C53" t="s">
+        <v>441</v>
+      </c>
+      <c r="D53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" t="s">
+        <v>208</v>
+      </c>
+      <c r="G53" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53">
+        <v>15300</v>
+      </c>
+      <c r="I53" s="1">
+        <v>46183</v>
+      </c>
+      <c r="J53">
+        <v>77833.64</v>
+      </c>
+      <c r="K53" t="s">
+        <v>343</v>
+      </c>
+      <c r="L53" t="s">
+        <v>19</v>
+      </c>
+      <c r="M53" t="s">
+        <v>196</v>
+      </c>
+      <c r="O53" t="s">
+        <v>197</v>
+      </c>
+      <c r="P53" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>199</v>
+      </c>
+      <c r="R53" t="s">
+        <v>20</v>
+      </c>
+      <c r="S53" t="s">
+        <v>34</v>
+      </c>
+      <c r="T53" t="s">
+        <v>171</v>
+      </c>
+      <c r="U53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>442</v>
+      </c>
+      <c r="B54" t="s">
+        <v>443</v>
+      </c>
+      <c r="C54" t="s">
+        <v>444</v>
+      </c>
+      <c r="D54" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" t="s">
+        <v>445</v>
+      </c>
+      <c r="G54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54">
+        <v>45759</v>
+      </c>
+      <c r="I54" s="1">
+        <v>46266</v>
+      </c>
+      <c r="J54">
+        <v>430</v>
+      </c>
+      <c r="K54" t="s">
+        <v>446</v>
+      </c>
+      <c r="L54" t="s">
+        <v>19</v>
+      </c>
+      <c r="O54" t="s">
+        <v>435</v>
+      </c>
+      <c r="P54" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>437</v>
+      </c>
+      <c r="R54" t="s">
+        <v>20</v>
+      </c>
+      <c r="S54" t="s">
+        <v>34</v>
+      </c>
+      <c r="T54" t="s">
+        <v>438</v>
+      </c>
+      <c r="U54" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>447</v>
+      </c>
+      <c r="B55" t="s">
+        <v>448</v>
+      </c>
+      <c r="C55" t="s">
+        <v>449</v>
+      </c>
+      <c r="D55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E55" t="s">
+        <v>433</v>
+      </c>
+      <c r="G55" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55">
+        <v>45756</v>
+      </c>
+      <c r="I55" s="1">
+        <v>46266</v>
+      </c>
+      <c r="J55">
+        <v>462.66</v>
+      </c>
+      <c r="K55" t="s">
+        <v>450</v>
+      </c>
+      <c r="L55" t="s">
+        <v>19</v>
+      </c>
+      <c r="O55" t="s">
+        <v>435</v>
+      </c>
+      <c r="P55" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>437</v>
+      </c>
+      <c r="R55" t="s">
+        <v>20</v>
+      </c>
+      <c r="S55" t="s">
+        <v>34</v>
+      </c>
+      <c r="T55" t="s">
+        <v>438</v>
+      </c>
+      <c r="U55" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>451</v>
+      </c>
+      <c r="B56" t="s">
+        <v>452</v>
+      </c>
+      <c r="C56" t="s">
+        <v>453</v>
+      </c>
+      <c r="D56" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" t="s">
+        <v>454</v>
+      </c>
+      <c r="G56" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56">
+        <v>433</v>
+      </c>
+      <c r="I56" s="1">
+        <v>46267</v>
+      </c>
+      <c r="J56">
+        <v>13040</v>
+      </c>
+      <c r="K56" t="s">
+        <v>455</v>
+      </c>
+      <c r="L56" t="s">
+        <v>19</v>
+      </c>
+      <c r="M56" t="s">
+        <v>45</v>
+      </c>
+      <c r="O56" t="s">
+        <v>456</v>
+      </c>
+      <c r="P56" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>458</v>
+      </c>
+      <c r="R56" t="s">
+        <v>20</v>
+      </c>
+      <c r="S56" t="s">
+        <v>34</v>
+      </c>
+      <c r="T56" t="s">
+        <v>52</v>
+      </c>
+      <c r="U56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" t="s">
+        <v>125</v>
+      </c>
+      <c r="C57" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" t="s">
+        <v>127</v>
+      </c>
+      <c r="G57" t="s">
+        <v>18</v>
+      </c>
+      <c r="H57" t="s">
+        <v>128</v>
+      </c>
+      <c r="I57" s="1">
+        <v>46237</v>
+      </c>
+      <c r="J57">
+        <v>14171.56</v>
+      </c>
+      <c r="K57" t="s">
+        <v>129</v>
+      </c>
+      <c r="L57" t="s">
+        <v>19</v>
+      </c>
+      <c r="M57" t="s">
+        <v>44</v>
+      </c>
+      <c r="O57" t="s">
+        <v>130</v>
+      </c>
+      <c r="P57" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>132</v>
+      </c>
+      <c r="R57" t="s">
+        <v>20</v>
+      </c>
+      <c r="S57" t="s">
+        <v>34</v>
+      </c>
+      <c r="T57" t="s">
+        <v>133</v>
+      </c>
+      <c r="U57" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>69</v>
+      </c>
+      <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" t="s">
+        <v>71</v>
+      </c>
+      <c r="D58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" t="s">
+        <v>72</v>
+      </c>
+      <c r="G58" t="s">
+        <v>18</v>
+      </c>
+      <c r="H58">
         <v>111828</v>
       </c>
-      <c r="I47" s="1">
+      <c r="I58" s="1">
         <v>46237</v>
       </c>
-      <c r="J47">
+      <c r="J58">
         <v>710.73</v>
       </c>
-      <c r="K47" t="s">
-        <v>86</v>
-      </c>
-      <c r="L47" t="s">
-        <v>19</v>
-      </c>
-      <c r="M47" t="s">
-        <v>56</v>
-      </c>
-      <c r="O47" t="s">
-        <v>87</v>
-      </c>
-      <c r="P47" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>88</v>
-      </c>
-      <c r="R47" t="s">
-        <v>20</v>
-      </c>
-      <c r="S47" t="s">
-        <v>44</v>
-      </c>
-      <c r="T47" t="s">
-        <v>62</v>
-      </c>
-      <c r="U47" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="I48" s="1"/>
-    </row>
-    <row r="49" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I49" s="1"/>
-    </row>
-    <row r="50" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I51" s="1"/>
-    </row>
-    <row r="52" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="9:13" x14ac:dyDescent="0.35">
-      <c r="I58" s="1"/>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="9:13" x14ac:dyDescent="0.35">
+      <c r="K58" t="s">
+        <v>73</v>
+      </c>
+      <c r="L58" t="s">
+        <v>19</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O58" t="s">
+        <v>74</v>
+      </c>
+      <c r="P58" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>75</v>
+      </c>
+      <c r="R58" t="s">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s">
+        <v>34</v>
+      </c>
+      <c r="T58" t="s">
+        <v>50</v>
+      </c>
+      <c r="U58" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="I59" s="1"/>
     </row>
-    <row r="60" spans="9:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="9:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="9:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="I62" s="1"/>
     </row>
-    <row r="63" spans="9:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="9:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="I64" s="1"/>
     </row>
     <row r="65" spans="9:13" x14ac:dyDescent="0.35">
